--- a/Clientes_25-26_frentes_padronizado.xlsx
+++ b/Clientes_25-26_frentes_padronizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas moreira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A2B9804-1A4F-4154-8162-BE7E6722FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518EAC3E-E776-462F-9D50-8E7D376502A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Brasil_Latam" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,11 @@
     <sheet name="Resumo_Atualizacoes" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Brasil_Latam!$A$1:$K$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Brasil_Latam!$A$1:$J$215</definedName>
     <definedName name="DadosExternos_1" localSheetId="2" hidden="1">'Fontes farol C&amp;D _ EB'!$A$1:$E$214</definedName>
     <definedName name="DadosExternos_1" localSheetId="1" hidden="1">Pulse!$A$1:$HR$157</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9494" uniqueCount="2232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9542" uniqueCount="2233">
   <si>
     <t>indice</t>
   </si>
@@ -8818,6 +8817,9 @@
   <si>
     <t>Pedra 26-27 alterados:</t>
   </si>
+  <si>
+    <t/>
+  </si>
 </sst>
 </file>
 
@@ -8848,7 +8850,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -8871,30 +8873,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9199,7 +9187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K215"/>
+  <dimension ref="A1:J215"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.81640625" bestFit="1" customWidth="1"/>
@@ -9211,7 +9199,7 @@
     <col min="8" max="8" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1917</v>
       </c>
@@ -9242,11 +9230,8 @@
       <c r="J1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>1919</v>
-      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>459</v>
       </c>
@@ -9256,9 +9241,8 @@
       <c r="C2" t="s">
         <v>1926</v>
       </c>
-      <c r="D2" t="str">
-        <f>IFERROR(VLOOKUP(B2,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B2,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D2" t="s">
+        <v>253</v>
       </c>
       <c r="E2" t="s">
         <v>235</v>
@@ -9279,7 +9263,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>459</v>
       </c>
@@ -9289,9 +9273,8 @@
       <c r="C3" t="s">
         <v>1926</v>
       </c>
-      <c r="D3" t="str">
-        <f>IFERROR(VLOOKUP(B3,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B3,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D3" t="s">
+        <v>253</v>
       </c>
       <c r="E3" t="s">
         <v>235</v>
@@ -9312,7 +9295,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>459</v>
       </c>
@@ -9322,9 +9305,8 @@
       <c r="C4" t="s">
         <v>1926</v>
       </c>
-      <c r="D4" t="str">
-        <f>IFERROR(VLOOKUP(B4,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B4,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D4" t="s">
+        <v>253</v>
       </c>
       <c r="E4" t="s">
         <v>1929</v>
@@ -9345,7 +9327,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>459</v>
       </c>
@@ -9355,9 +9337,8 @@
       <c r="C5" t="s">
         <v>1926</v>
       </c>
-      <c r="D5" t="str">
-        <f>IFERROR(VLOOKUP(B5,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B5,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D5" t="s">
+        <v>253</v>
       </c>
       <c r="E5" t="s">
         <v>1929</v>
@@ -9378,7 +9359,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>459</v>
       </c>
@@ -9388,9 +9369,8 @@
       <c r="C6" t="s">
         <v>1926</v>
       </c>
-      <c r="D6" t="str">
-        <f>IFERROR(VLOOKUP(B6,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B6,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D6" t="s">
+        <v>253</v>
       </c>
       <c r="E6" t="s">
         <v>1929</v>
@@ -9411,7 +9391,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>459</v>
       </c>
@@ -9421,9 +9401,8 @@
       <c r="C7" t="s">
         <v>1926</v>
       </c>
-      <c r="D7" t="str">
-        <f>IFERROR(VLOOKUP(B7,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B7,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D7" t="s">
+        <v>253</v>
       </c>
       <c r="E7" t="s">
         <v>1929</v>
@@ -9444,7 +9423,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>459</v>
       </c>
@@ -9454,10 +9433,6 @@
       <c r="C8" t="s">
         <v>1926</v>
       </c>
-      <c r="D8">
-        <f>IFERROR(VLOOKUP(B8,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B8,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E8" t="s">
         <v>1937</v>
       </c>
@@ -9477,7 +9452,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>459</v>
       </c>
@@ -9487,10 +9462,6 @@
       <c r="C9" t="s">
         <v>1926</v>
       </c>
-      <c r="D9">
-        <f>IFERROR(VLOOKUP(B9,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B9,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E9" t="s">
         <v>1940</v>
       </c>
@@ -9510,7 +9481,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>1515</v>
       </c>
@@ -9539,7 +9510,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>1515</v>
       </c>
@@ -9549,9 +9520,8 @@
       <c r="C11" t="s">
         <v>1926</v>
       </c>
-      <c r="D11" t="str">
-        <f>IFERROR(VLOOKUP(B11,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B11,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D11" t="s">
+        <v>253</v>
       </c>
       <c r="E11" t="s">
         <v>235</v>
@@ -9572,7 +9542,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>1515</v>
       </c>
@@ -9582,10 +9552,6 @@
       <c r="C12" t="s">
         <v>1926</v>
       </c>
-      <c r="D12">
-        <f>IFERROR(VLOOKUP(B12,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B12,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E12" t="s">
         <v>1929</v>
       </c>
@@ -9605,7 +9571,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1515</v>
       </c>
@@ -9615,10 +9581,6 @@
       <c r="C13" t="s">
         <v>1926</v>
       </c>
-      <c r="D13">
-        <f>IFERROR(VLOOKUP(B13,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B13,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E13" t="s">
         <v>1929</v>
       </c>
@@ -9638,7 +9600,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>798</v>
       </c>
@@ -9648,10 +9610,6 @@
       <c r="C14" t="s">
         <v>1926</v>
       </c>
-      <c r="D14">
-        <f>IFERROR(VLOOKUP(B14,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B14,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E14" t="s">
         <v>1929</v>
       </c>
@@ -9671,7 +9629,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>798</v>
       </c>
@@ -9681,9 +9639,8 @@
       <c r="C15" t="s">
         <v>1926</v>
       </c>
-      <c r="D15" t="str">
-        <f>IFERROR(VLOOKUP(B15,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B15,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D15" t="s">
+        <v>2232</v>
       </c>
       <c r="E15" t="s">
         <v>235</v>
@@ -9704,7 +9661,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>798</v>
       </c>
@@ -9714,9 +9671,8 @@
       <c r="C16" t="s">
         <v>1926</v>
       </c>
-      <c r="D16" t="str">
-        <f>IFERROR(VLOOKUP(B16,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B16,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D16" t="s">
+        <v>2232</v>
       </c>
       <c r="E16" t="s">
         <v>1937</v>
@@ -9747,9 +9703,8 @@
       <c r="C17" t="s">
         <v>1926</v>
       </c>
-      <c r="D17" t="str">
-        <f>IFERROR(VLOOKUP(B17,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B17,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D17" t="s">
+        <v>253</v>
       </c>
       <c r="E17" t="s">
         <v>235</v>
@@ -9780,9 +9735,8 @@
       <c r="C18" t="s">
         <v>1926</v>
       </c>
-      <c r="D18" t="str">
-        <f>IFERROR(VLOOKUP(B18,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B18,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D18" t="s">
+        <v>253</v>
       </c>
       <c r="E18" t="s">
         <v>235</v>
@@ -9813,10 +9767,6 @@
       <c r="C19" t="s">
         <v>1926</v>
       </c>
-      <c r="D19">
-        <f>IFERROR(VLOOKUP(B19,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B19,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E19" t="s">
         <v>1929</v>
       </c>
@@ -9846,10 +9796,6 @@
       <c r="C20" t="s">
         <v>1926</v>
       </c>
-      <c r="D20">
-        <f>IFERROR(VLOOKUP(B20,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B20,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E20" t="s">
         <v>1937</v>
       </c>
@@ -9879,10 +9825,6 @@
       <c r="C21" t="s">
         <v>1926</v>
       </c>
-      <c r="D21">
-        <f>IFERROR(VLOOKUP(B21,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B21,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E21" t="s">
         <v>1929</v>
       </c>
@@ -9906,10 +9848,6 @@
       <c r="C22" t="s">
         <v>1926</v>
       </c>
-      <c r="D22">
-        <f>IFERROR(VLOOKUP(B22,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B22,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E22" t="s">
         <v>1953</v>
       </c>
@@ -9933,10 +9871,6 @@
       <c r="C23" t="s">
         <v>1926</v>
       </c>
-      <c r="D23">
-        <f>IFERROR(VLOOKUP(B23,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B23,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E23" t="s">
         <v>1940</v>
       </c>
@@ -9960,10 +9894,6 @@
       <c r="C24" t="s">
         <v>1926</v>
       </c>
-      <c r="D24">
-        <f>IFERROR(VLOOKUP(B24,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B24,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E24" t="s">
         <v>1953</v>
       </c>
@@ -9987,10 +9917,6 @@
       <c r="C25" t="s">
         <v>1926</v>
       </c>
-      <c r="D25">
-        <f>IFERROR(VLOOKUP(B25,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B25,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E25" t="s">
         <v>1953</v>
       </c>
@@ -10014,10 +9940,6 @@
       <c r="C26" t="s">
         <v>1926</v>
       </c>
-      <c r="D26">
-        <f>IFERROR(VLOOKUP(B26,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B26,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E26" t="s">
         <v>1953</v>
       </c>
@@ -10041,10 +9963,6 @@
       <c r="C27" t="s">
         <v>1926</v>
       </c>
-      <c r="D27">
-        <f>IFERROR(VLOOKUP(B27,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B27,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E27" t="s">
         <v>235</v>
       </c>
@@ -10074,9 +9992,8 @@
       <c r="C28" t="s">
         <v>1926</v>
       </c>
-      <c r="D28" t="str">
-        <f>IFERROR(VLOOKUP(B28,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B28,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D28" t="s">
+        <v>253</v>
       </c>
       <c r="E28" t="s">
         <v>1929</v>
@@ -10107,9 +10024,8 @@
       <c r="C29" t="s">
         <v>1926</v>
       </c>
-      <c r="D29" t="str">
-        <f>IFERROR(VLOOKUP(B29,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B29,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D29" t="s">
+        <v>253</v>
       </c>
       <c r="E29" t="s">
         <v>304</v>
@@ -10137,10 +10053,6 @@
       <c r="C30" t="s">
         <v>1926</v>
       </c>
-      <c r="D30">
-        <f>IFERROR(VLOOKUP(B30,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B30,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E30" t="s">
         <v>1953</v>
       </c>
@@ -10167,10 +10079,6 @@
       <c r="C31" t="s">
         <v>1926</v>
       </c>
-      <c r="D31">
-        <f>IFERROR(VLOOKUP(B31,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B31,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E31" t="s">
         <v>1953</v>
       </c>
@@ -10197,9 +10105,8 @@
       <c r="C32" t="s">
         <v>1926</v>
       </c>
-      <c r="D32" t="str">
-        <f>IFERROR(VLOOKUP(B32,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B32,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D32" t="s">
+        <v>253</v>
       </c>
       <c r="E32" t="s">
         <v>235</v>
@@ -10227,10 +10134,6 @@
       <c r="C33" t="s">
         <v>1926</v>
       </c>
-      <c r="D33">
-        <f>IFERROR(VLOOKUP(B33,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B33,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E33" t="s">
         <v>1929</v>
       </c>
@@ -10257,9 +10160,8 @@
       <c r="C34" t="s">
         <v>1926</v>
       </c>
-      <c r="D34" t="str">
-        <f>IFERROR(VLOOKUP(B34,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B34,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D34" t="s">
+        <v>253</v>
       </c>
       <c r="E34" t="s">
         <v>235</v>
@@ -10290,10 +10192,6 @@
       <c r="C35" t="s">
         <v>1926</v>
       </c>
-      <c r="D35">
-        <f>IFERROR(VLOOKUP(B35,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B35,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E35" t="s">
         <v>1953</v>
       </c>
@@ -10323,10 +10221,6 @@
       <c r="C36" t="s">
         <v>1926</v>
       </c>
-      <c r="D36">
-        <f>IFERROR(VLOOKUP(B36,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B36,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E36" t="s">
         <v>1953</v>
       </c>
@@ -10356,10 +10250,6 @@
       <c r="C37" t="s">
         <v>1926</v>
       </c>
-      <c r="D37">
-        <f>IFERROR(VLOOKUP(B37,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B37,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E37" t="s">
         <v>1953</v>
       </c>
@@ -10389,10 +10279,6 @@
       <c r="C38" t="s">
         <v>1926</v>
       </c>
-      <c r="D38">
-        <f>IFERROR(VLOOKUP(B38,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B38,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E38" t="s">
         <v>235</v>
       </c>
@@ -10422,10 +10308,6 @@
       <c r="C39" t="s">
         <v>1926</v>
       </c>
-      <c r="D39">
-        <f>IFERROR(VLOOKUP(B39,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B39,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E39" t="s">
         <v>1953</v>
       </c>
@@ -10455,9 +10337,8 @@
       <c r="C40" t="s">
         <v>1926</v>
       </c>
-      <c r="D40" t="str">
-        <f>IFERROR(VLOOKUP(B40,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B40,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D40" t="s">
+        <v>253</v>
       </c>
       <c r="E40" t="s">
         <v>235</v>
@@ -10485,9 +10366,8 @@
       <c r="C41" t="s">
         <v>1926</v>
       </c>
-      <c r="D41" t="str">
-        <f>IFERROR(VLOOKUP(B41,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B41,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D41" t="s">
+        <v>253</v>
       </c>
       <c r="E41" t="s">
         <v>1929</v>
@@ -10515,9 +10395,8 @@
       <c r="C42" t="s">
         <v>1926</v>
       </c>
-      <c r="D42" t="str">
-        <f>IFERROR(VLOOKUP(B42,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B42,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D42" t="s">
+        <v>253</v>
       </c>
       <c r="E42" t="s">
         <v>235</v>
@@ -10545,9 +10424,8 @@
       <c r="C43" t="s">
         <v>1926</v>
       </c>
-      <c r="D43" t="str">
-        <f>IFERROR(VLOOKUP(B43,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B43,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D43" t="s">
+        <v>253</v>
       </c>
       <c r="E43" t="s">
         <v>235</v>
@@ -10575,10 +10453,6 @@
       <c r="C44" t="s">
         <v>1926</v>
       </c>
-      <c r="D44">
-        <f>IFERROR(VLOOKUP(B44,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B44,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E44" t="s">
         <v>1953</v>
       </c>
@@ -10605,10 +10479,6 @@
       <c r="C45" t="s">
         <v>1926</v>
       </c>
-      <c r="D45">
-        <f>IFERROR(VLOOKUP(B45,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B45,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E45" t="s">
         <v>1953</v>
       </c>
@@ -10635,10 +10505,6 @@
       <c r="C46" t="s">
         <v>1926</v>
       </c>
-      <c r="D46">
-        <f>IFERROR(VLOOKUP(B46,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B46,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E46" t="s">
         <v>1953</v>
       </c>
@@ -10665,10 +10531,6 @@
       <c r="C47" t="s">
         <v>1926</v>
       </c>
-      <c r="D47">
-        <f>IFERROR(VLOOKUP(B47,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B47,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E47" t="s">
         <v>1953</v>
       </c>
@@ -10695,9 +10557,8 @@
       <c r="C48" t="s">
         <v>1926</v>
       </c>
-      <c r="D48" t="str">
-        <f>IFERROR(VLOOKUP(B48,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B48,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D48" t="s">
+        <v>253</v>
       </c>
       <c r="E48" t="s">
         <v>235</v>
@@ -10728,10 +10589,6 @@
       <c r="C49" t="s">
         <v>1926</v>
       </c>
-      <c r="D49">
-        <f>IFERROR(VLOOKUP(B49,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B49,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E49" t="s">
         <v>1929</v>
       </c>
@@ -10761,10 +10618,6 @@
       <c r="C50" t="s">
         <v>1926</v>
       </c>
-      <c r="D50">
-        <f>IFERROR(VLOOKUP(B50,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B50,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E50" t="s">
         <v>235</v>
       </c>
@@ -10788,9 +10641,8 @@
       <c r="C51" t="s">
         <v>1926</v>
       </c>
-      <c r="D51" t="str">
-        <f>IFERROR(VLOOKUP(B51,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B51,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D51" t="s">
+        <v>253</v>
       </c>
       <c r="E51" t="s">
         <v>1929</v>
@@ -10815,10 +10667,6 @@
       <c r="C52" t="s">
         <v>1926</v>
       </c>
-      <c r="D52">
-        <f>IFERROR(VLOOKUP(B52,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B52,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E52" t="s">
         <v>235</v>
       </c>
@@ -10842,10 +10690,6 @@
       <c r="C53" t="s">
         <v>1926</v>
       </c>
-      <c r="D53">
-        <f>IFERROR(VLOOKUP(B53,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B53,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E53" t="s">
         <v>1953</v>
       </c>
@@ -10869,9 +10713,8 @@
       <c r="C54" t="s">
         <v>1926</v>
       </c>
-      <c r="D54" t="str">
-        <f>IFERROR(VLOOKUP(B54,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B54,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D54" t="s">
+        <v>2232</v>
       </c>
       <c r="E54" t="s">
         <v>235</v>
@@ -10925,10 +10768,6 @@
       <c r="C56" t="s">
         <v>1926</v>
       </c>
-      <c r="D56">
-        <f>IFERROR(VLOOKUP(B56,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B56,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E56" t="s">
         <v>1953</v>
       </c>
@@ -10958,10 +10797,6 @@
       <c r="C57" t="s">
         <v>1926</v>
       </c>
-      <c r="D57">
-        <f>IFERROR(VLOOKUP(B57,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B57,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E57" t="s">
         <v>1953</v>
       </c>
@@ -10991,10 +10826,6 @@
       <c r="C58" t="s">
         <v>1926</v>
       </c>
-      <c r="D58">
-        <f>IFERROR(VLOOKUP(B58,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B58,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E58" t="s">
         <v>1953</v>
       </c>
@@ -11024,10 +10855,6 @@
       <c r="C59" t="s">
         <v>1926</v>
       </c>
-      <c r="D59">
-        <f>IFERROR(VLOOKUP(B59,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B59,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E59" t="s">
         <v>1953</v>
       </c>
@@ -11057,10 +10884,6 @@
       <c r="C60" t="s">
         <v>1926</v>
       </c>
-      <c r="D60">
-        <f>IFERROR(VLOOKUP(B60,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B60,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E60" t="s">
         <v>1953</v>
       </c>
@@ -11090,10 +10913,6 @@
       <c r="C61" t="s">
         <v>1926</v>
       </c>
-      <c r="D61">
-        <f>IFERROR(VLOOKUP(B61,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B61,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E61" t="s">
         <v>1953</v>
       </c>
@@ -11155,9 +10974,8 @@
       <c r="C63" t="s">
         <v>1926</v>
       </c>
-      <c r="D63" t="str">
-        <f>IFERROR(VLOOKUP(B63,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B63,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D63" t="s">
+        <v>253</v>
       </c>
       <c r="E63" t="s">
         <v>1929</v>
@@ -11182,9 +11000,8 @@
       <c r="C64" t="s">
         <v>1926</v>
       </c>
-      <c r="D64" t="str">
-        <f>IFERROR(VLOOKUP(B64,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B64,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D64" t="s">
+        <v>253</v>
       </c>
       <c r="E64" t="s">
         <v>1929</v>
@@ -11209,10 +11026,6 @@
       <c r="C65" t="s">
         <v>1926</v>
       </c>
-      <c r="D65">
-        <f>IFERROR(VLOOKUP(B65,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B65,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E65" t="s">
         <v>1940</v>
       </c>
@@ -11236,9 +11049,8 @@
       <c r="C66" t="s">
         <v>1926</v>
       </c>
-      <c r="D66" t="str">
-        <f>IFERROR(VLOOKUP(B66,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B66,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D66" t="s">
+        <v>2232</v>
       </c>
       <c r="E66" t="s">
         <v>235</v>
@@ -11263,9 +11075,8 @@
       <c r="C67" t="s">
         <v>1926</v>
       </c>
-      <c r="D67" t="str">
-        <f>IFERROR(VLOOKUP(B67,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B67,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D67" t="s">
+        <v>2232</v>
       </c>
       <c r="E67" t="s">
         <v>1929</v>
@@ -11319,10 +11130,6 @@
       <c r="C69" t="s">
         <v>1926</v>
       </c>
-      <c r="D69">
-        <f>IFERROR(VLOOKUP(B69,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B69,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E69" t="s">
         <v>1953</v>
       </c>
@@ -11352,10 +11159,6 @@
       <c r="C70" t="s">
         <v>1926</v>
       </c>
-      <c r="D70">
-        <f>IFERROR(VLOOKUP(B70,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B70,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E70" t="s">
         <v>1940</v>
       </c>
@@ -11382,10 +11185,6 @@
       <c r="C71" t="s">
         <v>1926</v>
       </c>
-      <c r="D71">
-        <f>IFERROR(VLOOKUP(B71,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B71,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E71" t="s">
         <v>1929</v>
       </c>
@@ -11409,10 +11208,6 @@
       <c r="C72" t="s">
         <v>1926</v>
       </c>
-      <c r="D72">
-        <f>IFERROR(VLOOKUP(B72,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B72,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E72" t="s">
         <v>304</v>
       </c>
@@ -11436,10 +11231,6 @@
       <c r="C73" t="s">
         <v>1926</v>
       </c>
-      <c r="D73">
-        <f>IFERROR(VLOOKUP(B73,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B73,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E73" t="s">
         <v>304</v>
       </c>
@@ -11463,10 +11254,6 @@
       <c r="C74" t="s">
         <v>1926</v>
       </c>
-      <c r="D74">
-        <f>IFERROR(VLOOKUP(B74,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B74,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E74" t="s">
         <v>1929</v>
       </c>
@@ -11490,10 +11277,6 @@
       <c r="C75" t="s">
         <v>1926</v>
       </c>
-      <c r="D75">
-        <f>IFERROR(VLOOKUP(B75,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B75,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E75" t="s">
         <v>1929</v>
       </c>
@@ -11517,10 +11300,6 @@
       <c r="C76" t="s">
         <v>1926</v>
       </c>
-      <c r="D76">
-        <f>IFERROR(VLOOKUP(B76,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B76,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E76" t="s">
         <v>235</v>
       </c>
@@ -11550,10 +11329,6 @@
       <c r="C77" t="s">
         <v>1926</v>
       </c>
-      <c r="D77">
-        <f>IFERROR(VLOOKUP(B77,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B77,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E77" t="s">
         <v>235</v>
       </c>
@@ -11583,10 +11358,6 @@
       <c r="C78" t="s">
         <v>1926</v>
       </c>
-      <c r="D78">
-        <f>IFERROR(VLOOKUP(B78,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B78,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E78" t="s">
         <v>1953</v>
       </c>
@@ -11610,10 +11381,6 @@
       <c r="C79" t="s">
         <v>1926</v>
       </c>
-      <c r="D79">
-        <f>IFERROR(VLOOKUP(B79,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B79,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E79" t="s">
         <v>1953</v>
       </c>
@@ -11637,10 +11404,6 @@
       <c r="C80" t="s">
         <v>1926</v>
       </c>
-      <c r="D80">
-        <f>IFERROR(VLOOKUP(B80,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B80,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E80" t="s">
         <v>235</v>
       </c>
@@ -11670,9 +11433,8 @@
       <c r="C81" t="s">
         <v>1926</v>
       </c>
-      <c r="D81" t="str">
-        <f>IFERROR(VLOOKUP(B81,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B81,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D81" t="s">
+        <v>253</v>
       </c>
       <c r="E81" t="s">
         <v>235</v>
@@ -11703,10 +11465,6 @@
       <c r="C82" t="s">
         <v>1926</v>
       </c>
-      <c r="D82">
-        <f>IFERROR(VLOOKUP(B82,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B82,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E82" t="s">
         <v>235</v>
       </c>
@@ -11736,10 +11494,6 @@
       <c r="C83" t="s">
         <v>1926</v>
       </c>
-      <c r="D83">
-        <f>IFERROR(VLOOKUP(B83,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B83,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E83" t="s">
         <v>1953</v>
       </c>
@@ -11763,10 +11517,6 @@
       <c r="C84" t="s">
         <v>1926</v>
       </c>
-      <c r="D84">
-        <f>IFERROR(VLOOKUP(B84,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B84,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E84" t="s">
         <v>1953</v>
       </c>
@@ -11790,10 +11540,6 @@
       <c r="C85" t="s">
         <v>1926</v>
       </c>
-      <c r="D85">
-        <f>IFERROR(VLOOKUP(B85,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B85,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E85" t="s">
         <v>1953</v>
       </c>
@@ -11817,10 +11563,6 @@
       <c r="C86" t="s">
         <v>1926</v>
       </c>
-      <c r="D86">
-        <f>IFERROR(VLOOKUP(B86,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B86,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E86" t="s">
         <v>1953</v>
       </c>
@@ -11844,10 +11586,6 @@
       <c r="C87" t="s">
         <v>1926</v>
       </c>
-      <c r="D87">
-        <f>IFERROR(VLOOKUP(B87,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B87,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E87" t="s">
         <v>1953</v>
       </c>
@@ -11871,10 +11609,6 @@
       <c r="C88" t="s">
         <v>1926</v>
       </c>
-      <c r="D88">
-        <f>IFERROR(VLOOKUP(B88,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B88,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E88" t="s">
         <v>1953</v>
       </c>
@@ -11898,10 +11632,6 @@
       <c r="C89" t="s">
         <v>1926</v>
       </c>
-      <c r="D89">
-        <f>IFERROR(VLOOKUP(B89,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B89,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E89" t="s">
         <v>1953</v>
       </c>
@@ -11925,10 +11655,6 @@
       <c r="C90" t="s">
         <v>1926</v>
       </c>
-      <c r="D90">
-        <f>IFERROR(VLOOKUP(B90,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B90,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E90" t="s">
         <v>1953</v>
       </c>
@@ -11952,9 +11678,8 @@
       <c r="C91" t="s">
         <v>1926</v>
       </c>
-      <c r="D91" t="str">
-        <f>IFERROR(VLOOKUP(B91,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B91,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D91" t="s">
+        <v>253</v>
       </c>
       <c r="E91" t="s">
         <v>235</v>
@@ -11985,10 +11710,6 @@
       <c r="C92" t="s">
         <v>1926</v>
       </c>
-      <c r="D92">
-        <f>IFERROR(VLOOKUP(B92,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B92,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E92" t="s">
         <v>235</v>
       </c>
@@ -12018,10 +11739,6 @@
       <c r="C93" t="s">
         <v>1926</v>
       </c>
-      <c r="D93">
-        <f>IFERROR(VLOOKUP(B93,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B93,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E93" t="s">
         <v>1953</v>
       </c>
@@ -12045,10 +11762,6 @@
       <c r="C94" t="s">
         <v>1926</v>
       </c>
-      <c r="D94">
-        <f>IFERROR(VLOOKUP(B94,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B94,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E94" t="s">
         <v>1953</v>
       </c>
@@ -12072,10 +11785,6 @@
       <c r="C95" t="s">
         <v>1926</v>
       </c>
-      <c r="D95">
-        <f>IFERROR(VLOOKUP(B95,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B95,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E95" t="s">
         <v>1929</v>
       </c>
@@ -12099,10 +11808,6 @@
       <c r="C96" t="s">
         <v>1926</v>
       </c>
-      <c r="D96">
-        <f>IFERROR(VLOOKUP(B96,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B96,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E96" t="s">
         <v>1953</v>
       </c>
@@ -12126,10 +11831,6 @@
       <c r="C97" t="s">
         <v>1926</v>
       </c>
-      <c r="D97">
-        <f>IFERROR(VLOOKUP(B97,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B97,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E97" t="s">
         <v>1953</v>
       </c>
@@ -12153,10 +11854,6 @@
       <c r="C98" t="s">
         <v>1926</v>
       </c>
-      <c r="D98">
-        <f>IFERROR(VLOOKUP(B98,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B98,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E98" t="s">
         <v>1929</v>
       </c>
@@ -12180,10 +11877,6 @@
       <c r="C99" t="s">
         <v>1926</v>
       </c>
-      <c r="D99">
-        <f>IFERROR(VLOOKUP(B99,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B99,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E99" t="s">
         <v>1929</v>
       </c>
@@ -12207,10 +11900,6 @@
       <c r="C100" t="s">
         <v>1926</v>
       </c>
-      <c r="D100">
-        <f>IFERROR(VLOOKUP(B100,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B100,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E100" t="s">
         <v>1953</v>
       </c>
@@ -12234,10 +11923,6 @@
       <c r="C101" t="s">
         <v>1926</v>
       </c>
-      <c r="D101">
-        <f>IFERROR(VLOOKUP(B101,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B101,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E101" t="s">
         <v>1953</v>
       </c>
@@ -12261,10 +11946,6 @@
       <c r="C102" t="s">
         <v>1926</v>
       </c>
-      <c r="D102">
-        <f>IFERROR(VLOOKUP(B102,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B102,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E102" t="s">
         <v>1929</v>
       </c>
@@ -12288,10 +11969,6 @@
       <c r="C103" t="s">
         <v>1926</v>
       </c>
-      <c r="D103">
-        <f>IFERROR(VLOOKUP(B103,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B103,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E103" t="s">
         <v>1929</v>
       </c>
@@ -12315,9 +11992,8 @@
       <c r="C104" t="s">
         <v>1926</v>
       </c>
-      <c r="D104" t="str">
-        <f>IFERROR(VLOOKUP(B104,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B104,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D104" t="s">
+        <v>253</v>
       </c>
       <c r="E104" t="s">
         <v>304</v>
@@ -12342,10 +12018,6 @@
       <c r="C105" t="s">
         <v>1926</v>
       </c>
-      <c r="D105">
-        <f>IFERROR(VLOOKUP(B105,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B105,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E105" t="s">
         <v>1953</v>
       </c>
@@ -12369,10 +12041,6 @@
       <c r="C106" t="s">
         <v>1926</v>
       </c>
-      <c r="D106">
-        <f>IFERROR(VLOOKUP(B106,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B106,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E106" t="s">
         <v>1953</v>
       </c>
@@ -12396,10 +12064,6 @@
       <c r="C107" t="s">
         <v>1926</v>
       </c>
-      <c r="D107">
-        <f>IFERROR(VLOOKUP(B107,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B107,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E107" t="s">
         <v>1953</v>
       </c>
@@ -12423,10 +12087,6 @@
       <c r="C108" t="s">
         <v>1926</v>
       </c>
-      <c r="D108">
-        <f>IFERROR(VLOOKUP(B108,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B108,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E108" t="s">
         <v>1953</v>
       </c>
@@ -12473,10 +12133,6 @@
       <c r="C110" t="s">
         <v>1926</v>
       </c>
-      <c r="D110">
-        <f>IFERROR(VLOOKUP(B110,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B110,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E110" t="s">
         <v>235</v>
       </c>
@@ -12500,10 +12156,6 @@
       <c r="C111" t="s">
         <v>1926</v>
       </c>
-      <c r="D111">
-        <f>IFERROR(VLOOKUP(B111,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B111,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E111" t="s">
         <v>1953</v>
       </c>
@@ -12527,9 +12179,8 @@
       <c r="C112" t="s">
         <v>1926</v>
       </c>
-      <c r="D112" t="str">
-        <f>IFERROR(VLOOKUP(B112,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B112,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D112" t="s">
+        <v>253</v>
       </c>
       <c r="E112" t="s">
         <v>235</v>
@@ -12554,10 +12205,6 @@
       <c r="C113" t="s">
         <v>1926</v>
       </c>
-      <c r="D113">
-        <f>IFERROR(VLOOKUP(B113,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B113,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E113" t="s">
         <v>1953</v>
       </c>
@@ -12581,10 +12228,6 @@
       <c r="C114" t="s">
         <v>1926</v>
       </c>
-      <c r="D114">
-        <f>IFERROR(VLOOKUP(B114,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B114,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E114" t="s">
         <v>1953</v>
       </c>
@@ -12608,10 +12251,6 @@
       <c r="C115" t="s">
         <v>1926</v>
       </c>
-      <c r="D115">
-        <f>IFERROR(VLOOKUP(B115,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B115,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E115" t="s">
         <v>1929</v>
       </c>
@@ -12635,10 +12274,6 @@
       <c r="C116" t="s">
         <v>1926</v>
       </c>
-      <c r="D116">
-        <f>IFERROR(VLOOKUP(B116,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B116,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E116" t="s">
         <v>1929</v>
       </c>
@@ -12662,10 +12297,6 @@
       <c r="C117" t="s">
         <v>1926</v>
       </c>
-      <c r="D117">
-        <f>IFERROR(VLOOKUP(B117,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B117,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E117" t="s">
         <v>1929</v>
       </c>
@@ -12689,10 +12320,6 @@
       <c r="C118" t="s">
         <v>1926</v>
       </c>
-      <c r="D118">
-        <f>IFERROR(VLOOKUP(B118,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B118,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E118" t="s">
         <v>1929</v>
       </c>
@@ -12716,10 +12343,6 @@
       <c r="C119" t="s">
         <v>1926</v>
       </c>
-      <c r="D119">
-        <f>IFERROR(VLOOKUP(B119,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B119,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E119" t="s">
         <v>1929</v>
       </c>
@@ -12743,10 +12366,6 @@
       <c r="C120" t="s">
         <v>1926</v>
       </c>
-      <c r="D120">
-        <f>IFERROR(VLOOKUP(B120,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B120,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E120" t="s">
         <v>1929</v>
       </c>
@@ -12770,10 +12389,6 @@
       <c r="C121" t="s">
         <v>1926</v>
       </c>
-      <c r="D121">
-        <f>IFERROR(VLOOKUP(B121,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B121,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E121" t="s">
         <v>1929</v>
       </c>
@@ -12797,10 +12412,6 @@
       <c r="C122" t="s">
         <v>1926</v>
       </c>
-      <c r="D122">
-        <f>IFERROR(VLOOKUP(B122,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B122,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E122" t="s">
         <v>1929</v>
       </c>
@@ -12824,10 +12435,6 @@
       <c r="C123" t="s">
         <v>1926</v>
       </c>
-      <c r="D123">
-        <f>IFERROR(VLOOKUP(B123,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B123,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E123" t="s">
         <v>1929</v>
       </c>
@@ -12851,10 +12458,6 @@
       <c r="C124" t="s">
         <v>1926</v>
       </c>
-      <c r="D124">
-        <f>IFERROR(VLOOKUP(B124,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B124,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E124" t="s">
         <v>1929</v>
       </c>
@@ -12878,9 +12481,8 @@
       <c r="C125" t="s">
         <v>1926</v>
       </c>
-      <c r="D125" t="str">
-        <f>IFERROR(VLOOKUP(B125,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B125,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D125" t="s">
+        <v>2232</v>
       </c>
       <c r="E125" t="s">
         <v>1929</v>
@@ -12905,9 +12507,8 @@
       <c r="C126" t="s">
         <v>1926</v>
       </c>
-      <c r="D126" t="str">
-        <f>IFERROR(VLOOKUP(B126,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B126,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D126" t="s">
+        <v>2232</v>
       </c>
       <c r="E126" t="s">
         <v>1929</v>
@@ -12932,9 +12533,8 @@
       <c r="C127" t="s">
         <v>1926</v>
       </c>
-      <c r="D127" t="str">
-        <f>IFERROR(VLOOKUP(B127,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B127,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D127" t="s">
+        <v>2232</v>
       </c>
       <c r="E127" t="s">
         <v>1929</v>
@@ -12959,10 +12559,6 @@
       <c r="C128" t="s">
         <v>1926</v>
       </c>
-      <c r="D128">
-        <f>IFERROR(VLOOKUP(B128,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B128,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E128" t="s">
         <v>1929</v>
       </c>
@@ -12986,9 +12582,8 @@
       <c r="C129" t="s">
         <v>1926</v>
       </c>
-      <c r="D129" t="str">
-        <f>IFERROR(VLOOKUP(B129,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B129,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D129" t="s">
+        <v>253</v>
       </c>
       <c r="E129" t="s">
         <v>235</v>
@@ -13019,10 +12614,6 @@
       <c r="C130" t="s">
         <v>1926</v>
       </c>
-      <c r="D130">
-        <f>IFERROR(VLOOKUP(B130,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B130,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E130" t="s">
         <v>1929</v>
       </c>
@@ -13052,10 +12643,6 @@
       <c r="C131" t="s">
         <v>1926</v>
       </c>
-      <c r="D131">
-        <f>IFERROR(VLOOKUP(B131,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B131,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E131" t="s">
         <v>304</v>
       </c>
@@ -13079,10 +12666,6 @@
       <c r="C132" t="s">
         <v>1926</v>
       </c>
-      <c r="D132">
-        <f>IFERROR(VLOOKUP(B132,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B132,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E132" t="s">
         <v>1953</v>
       </c>
@@ -13106,10 +12689,6 @@
       <c r="C133" t="s">
         <v>1926</v>
       </c>
-      <c r="D133">
-        <f>IFERROR(VLOOKUP(B133,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B133,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E133" t="s">
         <v>1953</v>
       </c>
@@ -13133,10 +12712,6 @@
       <c r="C134" t="s">
         <v>1926</v>
       </c>
-      <c r="D134">
-        <f>IFERROR(VLOOKUP(B134,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B134,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E134" t="s">
         <v>235</v>
       </c>
@@ -13160,10 +12735,6 @@
       <c r="C135" t="s">
         <v>1926</v>
       </c>
-      <c r="D135">
-        <f>IFERROR(VLOOKUP(B135,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B135,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E135" t="s">
         <v>1953</v>
       </c>
@@ -13187,10 +12758,6 @@
       <c r="C136" t="s">
         <v>1926</v>
       </c>
-      <c r="D136">
-        <f>IFERROR(VLOOKUP(B136,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B136,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E136" t="s">
         <v>1953</v>
       </c>
@@ -13214,10 +12781,6 @@
       <c r="C137" t="s">
         <v>1926</v>
       </c>
-      <c r="D137">
-        <f>IFERROR(VLOOKUP(B137,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B137,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E137" t="s">
         <v>1953</v>
       </c>
@@ -13241,10 +12804,6 @@
       <c r="C138" t="s">
         <v>1926</v>
       </c>
-      <c r="D138">
-        <f>IFERROR(VLOOKUP(B138,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B138,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E138" t="s">
         <v>1929</v>
       </c>
@@ -13274,9 +12833,8 @@
       <c r="C139" t="s">
         <v>1926</v>
       </c>
-      <c r="D139" t="str">
-        <f>IFERROR(VLOOKUP(B139,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B139,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D139" t="s">
+        <v>253</v>
       </c>
       <c r="E139" t="s">
         <v>235</v>
@@ -13307,10 +12865,6 @@
       <c r="C140" t="s">
         <v>1926</v>
       </c>
-      <c r="D140">
-        <f>IFERROR(VLOOKUP(B140,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B140,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E140" t="s">
         <v>1929</v>
       </c>
@@ -13334,10 +12888,6 @@
       <c r="C141" t="s">
         <v>1926</v>
       </c>
-      <c r="D141">
-        <f>IFERROR(VLOOKUP(B141,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B141,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E141" t="s">
         <v>1953</v>
       </c>
@@ -13361,10 +12911,6 @@
       <c r="C142" t="s">
         <v>1926</v>
       </c>
-      <c r="D142">
-        <f>IFERROR(VLOOKUP(B142,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B142,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E142" t="s">
         <v>1929</v>
       </c>
@@ -13417,9 +12963,8 @@
       <c r="C144" t="s">
         <v>1926</v>
       </c>
-      <c r="D144" t="str">
-        <f>IFERROR(VLOOKUP(B144,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B144,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D144" t="s">
+        <v>2232</v>
       </c>
       <c r="E144" t="s">
         <v>235</v>
@@ -13444,9 +12989,8 @@
       <c r="C145" t="s">
         <v>1926</v>
       </c>
-      <c r="D145" t="str">
-        <f>IFERROR(VLOOKUP(B145,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B145,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D145" t="s">
+        <v>253</v>
       </c>
       <c r="E145" t="s">
         <v>235</v>
@@ -13471,10 +13015,6 @@
       <c r="C146" t="s">
         <v>1926</v>
       </c>
-      <c r="D146">
-        <f>IFERROR(VLOOKUP(B146,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B146,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E146" t="s">
         <v>1953</v>
       </c>
@@ -13498,10 +13038,6 @@
       <c r="C147" t="s">
         <v>1926</v>
       </c>
-      <c r="D147">
-        <f>IFERROR(VLOOKUP(B147,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B147,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E147" t="s">
         <v>1929</v>
       </c>
@@ -13525,10 +13061,6 @@
       <c r="C148" t="s">
         <v>1926</v>
       </c>
-      <c r="D148">
-        <f>IFERROR(VLOOKUP(B148,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B148,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E148" t="s">
         <v>1953</v>
       </c>
@@ -13552,9 +13084,8 @@
       <c r="C149" t="s">
         <v>1926</v>
       </c>
-      <c r="D149" t="str">
-        <f>IFERROR(VLOOKUP(B149,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B149,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D149" t="s">
+        <v>253</v>
       </c>
       <c r="E149" t="s">
         <v>1929</v>
@@ -13579,9 +13110,8 @@
       <c r="C150" t="s">
         <v>1926</v>
       </c>
-      <c r="D150" t="str">
-        <f>IFERROR(VLOOKUP(B150,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B150,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D150" t="s">
+        <v>253</v>
       </c>
       <c r="E150" t="s">
         <v>1929</v>
@@ -13606,10 +13136,6 @@
       <c r="C151" t="s">
         <v>1926</v>
       </c>
-      <c r="D151">
-        <f>IFERROR(VLOOKUP(B151,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B151,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E151" t="s">
         <v>1953</v>
       </c>
@@ -13633,10 +13159,6 @@
       <c r="C152" t="s">
         <v>1926</v>
       </c>
-      <c r="D152">
-        <f>IFERROR(VLOOKUP(B152,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B152,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E152" t="s">
         <v>1953</v>
       </c>
@@ -13660,9 +13182,8 @@
       <c r="C153" t="s">
         <v>1926</v>
       </c>
-      <c r="D153" t="str">
-        <f>IFERROR(VLOOKUP(B153,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B153,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D153" t="s">
+        <v>253</v>
       </c>
       <c r="E153" t="s">
         <v>1929</v>
@@ -13687,9 +13208,8 @@
       <c r="C154" t="s">
         <v>1926</v>
       </c>
-      <c r="D154" t="str">
-        <f>IFERROR(VLOOKUP(B154,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B154,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D154" t="s">
+        <v>253</v>
       </c>
       <c r="E154" t="s">
         <v>1929</v>
@@ -13714,9 +13234,8 @@
       <c r="C155" t="s">
         <v>1926</v>
       </c>
-      <c r="D155" t="str">
-        <f>IFERROR(VLOOKUP(B155,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B155,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D155" t="s">
+        <v>2232</v>
       </c>
       <c r="E155" t="s">
         <v>1929</v>
@@ -13741,10 +13260,6 @@
       <c r="C156" t="s">
         <v>1926</v>
       </c>
-      <c r="D156">
-        <f>IFERROR(VLOOKUP(B156,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B156,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E156" t="s">
         <v>1953</v>
       </c>
@@ -13768,10 +13283,6 @@
       <c r="C157" t="s">
         <v>1926</v>
       </c>
-      <c r="D157">
-        <f>IFERROR(VLOOKUP(B157,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B157,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E157" t="s">
         <v>1953</v>
       </c>
@@ -13795,10 +13306,6 @@
       <c r="C158" t="s">
         <v>1926</v>
       </c>
-      <c r="D158">
-        <f>IFERROR(VLOOKUP(B158,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B158,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E158" t="s">
         <v>1953</v>
       </c>
@@ -13822,10 +13329,6 @@
       <c r="C159" t="s">
         <v>1926</v>
       </c>
-      <c r="D159">
-        <f>IFERROR(VLOOKUP(B159,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B159,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E159" t="s">
         <v>1953</v>
       </c>
@@ -13849,9 +13352,8 @@
       <c r="C160" t="s">
         <v>1926</v>
       </c>
-      <c r="D160" t="str">
-        <f>IFERROR(VLOOKUP(B160,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B160,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D160" t="s">
+        <v>253</v>
       </c>
       <c r="E160" t="s">
         <v>235</v>
@@ -13879,9 +13381,8 @@
       <c r="C161" t="s">
         <v>1926</v>
       </c>
-      <c r="D161" t="str">
-        <f>IFERROR(VLOOKUP(B161,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B161,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D161" t="s">
+        <v>253</v>
       </c>
       <c r="E161" t="s">
         <v>1929</v>
@@ -13909,10 +13410,6 @@
       <c r="C162" t="s">
         <v>1926</v>
       </c>
-      <c r="D162">
-        <f>IFERROR(VLOOKUP(B162,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B162,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E162" t="s">
         <v>304</v>
       </c>
@@ -13942,10 +13439,6 @@
       <c r="C163" t="s">
         <v>1926</v>
       </c>
-      <c r="D163">
-        <f>IFERROR(VLOOKUP(B163,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B163,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E163" t="s">
         <v>1953</v>
       </c>
@@ -13969,10 +13462,6 @@
       <c r="C164" t="s">
         <v>1926</v>
       </c>
-      <c r="D164">
-        <f>IFERROR(VLOOKUP(B164,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B164,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E164" t="s">
         <v>1953</v>
       </c>
@@ -13996,10 +13485,6 @@
       <c r="C165" t="s">
         <v>1926</v>
       </c>
-      <c r="D165">
-        <f>IFERROR(VLOOKUP(B165,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B165,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E165" t="s">
         <v>1953</v>
       </c>
@@ -14023,10 +13508,6 @@
       <c r="C166" t="s">
         <v>1926</v>
       </c>
-      <c r="D166">
-        <f>IFERROR(VLOOKUP(B166,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B166,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E166" t="s">
         <v>1953</v>
       </c>
@@ -14050,10 +13531,6 @@
       <c r="C167" t="s">
         <v>1926</v>
       </c>
-      <c r="D167">
-        <f>IFERROR(VLOOKUP(B167,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B167,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E167" t="s">
         <v>1929</v>
       </c>
@@ -14077,10 +13554,6 @@
       <c r="C168" t="s">
         <v>1926</v>
       </c>
-      <c r="D168">
-        <f>IFERROR(VLOOKUP(B168,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B168,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E168" t="s">
         <v>1929</v>
       </c>
@@ -14104,10 +13577,6 @@
       <c r="C169" t="s">
         <v>1926</v>
       </c>
-      <c r="D169">
-        <f>IFERROR(VLOOKUP(B169,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B169,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E169" t="s">
         <v>1937</v>
       </c>
@@ -14137,10 +13606,6 @@
       <c r="C170" t="s">
         <v>1926</v>
       </c>
-      <c r="D170">
-        <f>IFERROR(VLOOKUP(B170,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B170,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E170" t="s">
         <v>1953</v>
       </c>
@@ -14164,10 +13629,6 @@
       <c r="C171" t="s">
         <v>1926</v>
       </c>
-      <c r="D171">
-        <f>IFERROR(VLOOKUP(B171,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B171,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E171" t="s">
         <v>1929</v>
       </c>
@@ -14191,10 +13652,6 @@
       <c r="C172" t="s">
         <v>1926</v>
       </c>
-      <c r="D172">
-        <f>IFERROR(VLOOKUP(B172,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B172,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E172" t="s">
         <v>1929</v>
       </c>
@@ -14218,10 +13675,6 @@
       <c r="C173" t="s">
         <v>1926</v>
       </c>
-      <c r="D173">
-        <f>IFERROR(VLOOKUP(B173,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B173,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E173" t="s">
         <v>1953</v>
       </c>
@@ -14245,10 +13698,6 @@
       <c r="C174" t="s">
         <v>1926</v>
       </c>
-      <c r="D174">
-        <f>IFERROR(VLOOKUP(B174,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B174,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E174" t="s">
         <v>1953</v>
       </c>
@@ -14272,10 +13721,6 @@
       <c r="C175" t="s">
         <v>1926</v>
       </c>
-      <c r="D175">
-        <f>IFERROR(VLOOKUP(B175,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B175,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E175" t="s">
         <v>304</v>
       </c>
@@ -14299,10 +13744,6 @@
       <c r="C176" t="s">
         <v>1926</v>
       </c>
-      <c r="D176">
-        <f>IFERROR(VLOOKUP(B176,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B176,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E176" t="s">
         <v>1929</v>
       </c>
@@ -14326,10 +13767,6 @@
       <c r="C177" t="s">
         <v>1926</v>
       </c>
-      <c r="D177">
-        <f>IFERROR(VLOOKUP(B177,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B177,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E177" t="s">
         <v>304</v>
       </c>
@@ -14359,9 +13796,8 @@
       <c r="C178" t="s">
         <v>1926</v>
       </c>
-      <c r="D178" t="str">
-        <f>IFERROR(VLOOKUP(B178,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B178,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D178" t="s">
+        <v>253</v>
       </c>
       <c r="E178" t="s">
         <v>235</v>
@@ -14392,10 +13828,6 @@
       <c r="C179" t="s">
         <v>1926</v>
       </c>
-      <c r="D179">
-        <f>IFERROR(VLOOKUP(B179,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B179,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E179" t="s">
         <v>304</v>
       </c>
@@ -14425,10 +13857,6 @@
       <c r="C180" t="s">
         <v>1926</v>
       </c>
-      <c r="D180">
-        <f>IFERROR(VLOOKUP(B180,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B180,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E180" t="s">
         <v>1929</v>
       </c>
@@ -14452,10 +13880,6 @@
       <c r="C181" t="s">
         <v>1926</v>
       </c>
-      <c r="D181">
-        <f>IFERROR(VLOOKUP(B181,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B181,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E181" t="s">
         <v>1929</v>
       </c>
@@ -14479,10 +13903,6 @@
       <c r="C182" t="s">
         <v>1926</v>
       </c>
-      <c r="D182">
-        <f>IFERROR(VLOOKUP(B182,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B182,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E182" t="s">
         <v>1929</v>
       </c>
@@ -14506,10 +13926,6 @@
       <c r="C183" t="s">
         <v>1926</v>
       </c>
-      <c r="D183">
-        <f>IFERROR(VLOOKUP(B183,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B183,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E183" t="s">
         <v>1929</v>
       </c>
@@ -14533,10 +13949,6 @@
       <c r="C184" t="s">
         <v>1926</v>
       </c>
-      <c r="D184">
-        <f>IFERROR(VLOOKUP(B184,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B184,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E184" t="s">
         <v>1929</v>
       </c>
@@ -14560,10 +13972,6 @@
       <c r="C185" t="s">
         <v>1926</v>
       </c>
-      <c r="D185">
-        <f>IFERROR(VLOOKUP(B185,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B185,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E185" t="s">
         <v>1929</v>
       </c>
@@ -14587,10 +13995,6 @@
       <c r="C186" t="s">
         <v>1926</v>
       </c>
-      <c r="D186">
-        <f>IFERROR(VLOOKUP(B186,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B186,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E186" t="s">
         <v>1929</v>
       </c>
@@ -14614,10 +14018,6 @@
       <c r="C187" t="s">
         <v>1926</v>
       </c>
-      <c r="D187">
-        <f>IFERROR(VLOOKUP(B187,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B187,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E187" t="s">
         <v>1929</v>
       </c>
@@ -14641,10 +14041,6 @@
       <c r="C188" t="s">
         <v>1926</v>
       </c>
-      <c r="D188">
-        <f>IFERROR(VLOOKUP(B188,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B188,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E188" t="s">
         <v>1929</v>
       </c>
@@ -14668,10 +14064,6 @@
       <c r="C189" t="s">
         <v>1926</v>
       </c>
-      <c r="D189">
-        <f>IFERROR(VLOOKUP(B189,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B189,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E189" t="s">
         <v>1929</v>
       </c>
@@ -14695,9 +14087,8 @@
       <c r="C190" t="s">
         <v>1926</v>
       </c>
-      <c r="D190" t="str">
-        <f>IFERROR(VLOOKUP(B190,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B190,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D190" t="s">
+        <v>2232</v>
       </c>
       <c r="E190" t="s">
         <v>1929</v>
@@ -14722,9 +14113,8 @@
       <c r="C191" t="s">
         <v>1926</v>
       </c>
-      <c r="D191" t="str">
-        <f>IFERROR(VLOOKUP(B191,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B191,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v/>
+      <c r="D191" t="s">
+        <v>2232</v>
       </c>
       <c r="E191" t="s">
         <v>1929</v>
@@ -14749,10 +14139,6 @@
       <c r="C192" t="s">
         <v>1926</v>
       </c>
-      <c r="D192">
-        <f>IFERROR(VLOOKUP(B192,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B192,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E192" t="s">
         <v>1929</v>
       </c>
@@ -14776,10 +14162,6 @@
       <c r="C193" t="s">
         <v>1926</v>
       </c>
-      <c r="D193">
-        <f>IFERROR(VLOOKUP(B193,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B193,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E193" t="s">
         <v>1929</v>
       </c>
@@ -14803,10 +14185,6 @@
       <c r="C194" t="s">
         <v>1926</v>
       </c>
-      <c r="D194">
-        <f>IFERROR(VLOOKUP(B194,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B194,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E194" t="s">
         <v>1929</v>
       </c>
@@ -14830,10 +14208,6 @@
       <c r="C195" t="s">
         <v>1926</v>
       </c>
-      <c r="D195">
-        <f>IFERROR(VLOOKUP(B195,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B195,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E195" t="s">
         <v>1929</v>
       </c>
@@ -14857,10 +14231,6 @@
       <c r="C196" t="s">
         <v>1926</v>
       </c>
-      <c r="D196">
-        <f>IFERROR(VLOOKUP(B196,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B196,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E196" t="s">
         <v>235</v>
       </c>
@@ -14890,10 +14260,6 @@
       <c r="C197" t="s">
         <v>1926</v>
       </c>
-      <c r="D197">
-        <f>IFERROR(VLOOKUP(B197,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B197,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E197" t="s">
         <v>1929</v>
       </c>
@@ -14917,10 +14283,6 @@
       <c r="C198" t="s">
         <v>1926</v>
       </c>
-      <c r="D198">
-        <f>IFERROR(VLOOKUP(B198,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B198,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E198" t="s">
         <v>1929</v>
       </c>
@@ -14944,10 +14306,6 @@
       <c r="C199" t="s">
         <v>1926</v>
       </c>
-      <c r="D199">
-        <f>IFERROR(VLOOKUP(B199,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B199,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E199" t="s">
         <v>1929</v>
       </c>
@@ -14974,10 +14332,6 @@
       <c r="C200" t="s">
         <v>1926</v>
       </c>
-      <c r="D200">
-        <f>IFERROR(VLOOKUP(B200,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B200,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E200" t="s">
         <v>1953</v>
       </c>
@@ -15001,10 +14355,6 @@
       <c r="C201" t="s">
         <v>1926</v>
       </c>
-      <c r="D201">
-        <f>IFERROR(VLOOKUP(B201,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B201,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E201" t="s">
         <v>1940</v>
       </c>
@@ -15028,10 +14378,6 @@
       <c r="C202" t="s">
         <v>1926</v>
       </c>
-      <c r="D202">
-        <f>IFERROR(VLOOKUP(B202,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B202,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E202" t="s">
         <v>1929</v>
       </c>
@@ -15055,9 +14401,8 @@
       <c r="C203" t="s">
         <v>1926</v>
       </c>
-      <c r="D203" t="str">
-        <f>IFERROR(VLOOKUP(B203,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B203,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D203" t="s">
+        <v>253</v>
       </c>
       <c r="E203" t="s">
         <v>1929</v>
@@ -15088,10 +14433,6 @@
       <c r="C204" t="s">
         <v>1926</v>
       </c>
-      <c r="D204">
-        <f>IFERROR(VLOOKUP(B204,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B204,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E204" t="s">
         <v>1929</v>
       </c>
@@ -15115,10 +14456,6 @@
       <c r="C205" t="s">
         <v>1926</v>
       </c>
-      <c r="D205">
-        <f>IFERROR(VLOOKUP(B205,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B205,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E205" t="s">
         <v>1929</v>
       </c>
@@ -15142,10 +14479,6 @@
       <c r="C206" t="s">
         <v>1926</v>
       </c>
-      <c r="D206">
-        <f>IFERROR(VLOOKUP(B206,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B206,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E206" t="s">
         <v>1940</v>
       </c>
@@ -15169,10 +14502,6 @@
       <c r="C207" t="s">
         <v>1926</v>
       </c>
-      <c r="D207">
-        <f>IFERROR(VLOOKUP(B207,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B207,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E207" t="s">
         <v>1929</v>
       </c>
@@ -15196,10 +14525,6 @@
       <c r="C208" t="s">
         <v>1926</v>
       </c>
-      <c r="D208">
-        <f>IFERROR(VLOOKUP(B208,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B208,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E208" t="s">
         <v>1953</v>
       </c>
@@ -15223,10 +14548,6 @@
       <c r="C209" t="s">
         <v>1926</v>
       </c>
-      <c r="D209">
-        <f>IFERROR(VLOOKUP(B209,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B209,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E209" t="s">
         <v>1953</v>
       </c>
@@ -15250,10 +14571,6 @@
       <c r="C210" t="s">
         <v>1926</v>
       </c>
-      <c r="D210">
-        <f>IFERROR(VLOOKUP(B210,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B210,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E210" t="s">
         <v>1929</v>
       </c>
@@ -15277,10 +14594,6 @@
       <c r="C211" t="s">
         <v>1926</v>
       </c>
-      <c r="D211">
-        <f>IFERROR(VLOOKUP(B211,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B211,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E211" t="s">
         <v>1953</v>
       </c>
@@ -15304,10 +14617,6 @@
       <c r="C212" t="s">
         <v>1926</v>
       </c>
-      <c r="D212">
-        <f>IFERROR(VLOOKUP(B212,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B212,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E212" t="s">
         <v>1953</v>
       </c>
@@ -15331,10 +14640,6 @@
       <c r="C213" t="s">
         <v>1926</v>
       </c>
-      <c r="D213">
-        <f>IFERROR(VLOOKUP(B213,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B213,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E213" t="s">
         <v>1953</v>
       </c>
@@ -15364,9 +14669,8 @@
       <c r="C214" t="s">
         <v>1926</v>
       </c>
-      <c r="D214" t="str">
-        <f>IFERROR(VLOOKUP(B214,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B214,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>Verde</v>
+      <c r="D214" t="s">
+        <v>253</v>
       </c>
       <c r="E214" t="s">
         <v>304</v>
@@ -15397,10 +14701,6 @@
       <c r="C215" t="s">
         <v>1926</v>
       </c>
-      <c r="D215">
-        <f>IFERROR(VLOOKUP(B215,Pulse!J:BB,45,FALSE),IFERROR(VLOOKUP(B215,'Fontes farol C&amp;D _ EB'!B:E,4,FALSE),""))</f>
-        <v>0</v>
-      </c>
       <c r="E215" t="s">
         <v>1953</v>
       </c>
@@ -15415,7 +14715,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K215" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J215" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Clientes_25-26_frentes_padronizado.xlsx
+++ b/Clientes_25-26_frentes_padronizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas moreira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC6E9EF-14C9-4BB3-B356-B02CF205D00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAADF3C-5D61-4901-A60D-4C685AE0ADF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Brasil_Latam" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Brasil_Latam!$A$1:$K$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Brasil_Latam!$A$1:$J$216</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="401">
   <si>
     <t>Pedra</t>
   </si>
@@ -340,9 +340,6 @@
     <t>PepsiCo - PepsiCo First Gen 2025 - Ciclo 25/26</t>
   </si>
   <si>
-    <t>Empresa relacionada - Nomes</t>
-  </si>
-  <si>
     <t>Nome</t>
   </si>
   <si>
@@ -1244,6 +1241,9 @@
   </si>
   <si>
     <t>Sebrae - Links Facet5 Fevereiro 2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Programa de Estágio Bracell Ciclo 26/27</t>
@@ -1278,7 +1278,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1301,17 +1301,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1321,7 +1310,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1628,7 +1617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K216"/>
+  <dimension ref="A1:J216"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.81640625" bestFit="1" customWidth="1"/>
@@ -1640,59 +1629,56 @@
     <col min="8" max="8" width="15.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>109</v>
       </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>110</v>
-      </c>
-      <c r="F2" t="s">
-        <v>111</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1701,30 +1687,30 @@
         <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" t="s">
         <v>112</v>
-      </c>
-      <c r="C3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" t="s">
-        <v>113</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1733,30 +1719,30 @@
         <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" t="s">
         <v>114</v>
-      </c>
-      <c r="C4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" t="s">
-        <v>115</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1765,30 +1751,30 @@
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1797,30 +1783,30 @@
         <v>8</v>
       </c>
       <c r="I5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
         <v>120</v>
       </c>
-      <c r="C6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>121</v>
-      </c>
-      <c r="F6" t="s">
-        <v>122</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1829,30 +1815,30 @@
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
         <v>117</v>
       </c>
-      <c r="C7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>118</v>
-      </c>
-      <c r="F7" t="s">
-        <v>119</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1861,13 +1847,13 @@
         <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1875,7 +1861,7 @@
         <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -1893,13 +1879,13 @@
         <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1907,7 +1893,7 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1925,13 +1911,13 @@
         <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -1939,7 +1925,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1957,30 +1943,30 @@
         <v>4</v>
       </c>
       <c r="I10" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" t="s">
         <v>123</v>
       </c>
-      <c r="J10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -1989,30 +1975,30 @@
         <v>4</v>
       </c>
       <c r="I11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J11" t="s">
         <v>123</v>
       </c>
-      <c r="J11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -2021,13 +2007,13 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" t="s">
         <v>123</v>
       </c>
-      <c r="J12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -2035,7 +2021,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -2053,13 +2039,13 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" t="s">
         <v>123</v>
       </c>
-      <c r="J13" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2067,7 +2053,7 @@
         <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -2085,30 +2071,30 @@
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -2117,30 +2103,30 @@
         <v>3</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" t="s">
         <v>118</v>
-      </c>
-      <c r="F16" t="s">
-        <v>119</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -2149,7 +2135,7 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
@@ -2160,10 +2146,10 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
@@ -2181,7 +2167,7 @@
         <v>3</v>
       </c>
       <c r="I17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J17" t="s">
         <v>4</v>
@@ -2195,7 +2181,7 @@
         <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
@@ -2213,7 +2199,7 @@
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J18" t="s">
         <v>4</v>
@@ -2224,19 +2210,19 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
         <v>110</v>
-      </c>
-      <c r="F19" t="s">
-        <v>111</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -2245,7 +2231,7 @@
         <v>4</v>
       </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J19" t="s">
         <v>4</v>
@@ -2256,19 +2242,19 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" t="s">
         <v>129</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" t="s">
-        <v>130</v>
       </c>
       <c r="G20">
         <v>3</v>
@@ -2277,7 +2263,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J20" t="s">
         <v>4</v>
@@ -2285,22 +2271,22 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
         <v>133</v>
       </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>134</v>
-      </c>
-      <c r="F21" t="s">
-        <v>135</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -2311,22 +2297,22 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
         <v>131</v>
       </c>
-      <c r="B22" t="s">
-        <v>132</v>
-      </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
         <v>110</v>
-      </c>
-      <c r="F22" t="s">
-        <v>111</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -2340,19 +2326,19 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" t="s">
         <v>139</v>
-      </c>
-      <c r="C23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F23" t="s">
-        <v>140</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2366,16 +2352,16 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -2392,19 +2378,19 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" t="s">
         <v>137</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" t="s">
-        <v>134</v>
-      </c>
-      <c r="F25" t="s">
-        <v>138</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -2418,19 +2404,19 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26" t="s">
+        <v>133</v>
+      </c>
+      <c r="F26" t="s">
         <v>134</v>
-      </c>
-      <c r="F26" t="s">
-        <v>135</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -2444,10 +2430,10 @@
         <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -2465,10 +2451,10 @@
         <v>2</v>
       </c>
       <c r="I27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
@@ -2476,19 +2462,19 @@
         <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -2497,10 +2483,10 @@
         <v>2</v>
       </c>
       <c r="I28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
@@ -2511,7 +2497,7 @@
         <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
@@ -2529,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="I29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
@@ -2537,19 +2523,19 @@
         <v>59</v>
       </c>
       <c r="B30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" t="s">
         <v>147</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" t="s">
-        <v>134</v>
-      </c>
-      <c r="F30" t="s">
-        <v>148</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -2558,7 +2544,7 @@
         <v>3</v>
       </c>
       <c r="I30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
@@ -2566,19 +2552,19 @@
         <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" t="s">
         <v>134</v>
-      </c>
-      <c r="F31" t="s">
-        <v>135</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2587,7 +2573,7 @@
         <v>3</v>
       </c>
       <c r="I31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
@@ -2598,7 +2584,7 @@
         <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -2624,19 +2610,19 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" t="s">
         <v>149</v>
-      </c>
-      <c r="C33" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" t="s">
-        <v>110</v>
-      </c>
-      <c r="F33" t="s">
-        <v>150</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2653,19 +2639,19 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" t="s">
         <v>134</v>
-      </c>
-      <c r="F34" t="s">
-        <v>135</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -2674,7 +2660,7 @@
         <v>4</v>
       </c>
       <c r="I34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J34" t="s">
         <v>26</v>
@@ -2688,7 +2674,7 @@
         <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
@@ -2706,7 +2692,7 @@
         <v>4</v>
       </c>
       <c r="I35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J35" t="s">
         <v>26</v>
@@ -2717,19 +2703,19 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" t="s">
         <v>134</v>
-      </c>
-      <c r="F36" t="s">
-        <v>135</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2738,7 +2724,7 @@
         <v>4</v>
       </c>
       <c r="I36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J36" t="s">
         <v>26</v>
@@ -2749,19 +2735,19 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
       </c>
       <c r="E37" t="s">
+        <v>133</v>
+      </c>
+      <c r="F37" t="s">
         <v>134</v>
-      </c>
-      <c r="F37" t="s">
-        <v>135</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2770,7 +2756,7 @@
         <v>4</v>
       </c>
       <c r="I37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J37" t="s">
         <v>26</v>
@@ -2781,10 +2767,10 @@
         <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -2802,7 +2788,7 @@
         <v>2</v>
       </c>
       <c r="I38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J38" t="s">
         <v>4</v>
@@ -2813,19 +2799,19 @@
         <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -2834,7 +2820,7 @@
         <v>2</v>
       </c>
       <c r="I39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J39" t="s">
         <v>4</v>
@@ -2845,19 +2831,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2866,7 +2852,7 @@
         <v>2</v>
       </c>
       <c r="I40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
@@ -2877,7 +2863,7 @@
         <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -2895,7 +2881,7 @@
         <v>2</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
@@ -2906,7 +2892,7 @@
         <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -2924,7 +2910,7 @@
         <v>6</v>
       </c>
       <c r="J42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
@@ -2935,7 +2921,7 @@
         <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -2953,7 +2939,7 @@
         <v>6</v>
       </c>
       <c r="J43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
@@ -2961,19 +2947,19 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
       <c r="E44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s">
         <v>134</v>
-      </c>
-      <c r="F44" t="s">
-        <v>135</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2982,7 +2968,7 @@
         <v>6</v>
       </c>
       <c r="J44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
@@ -2990,19 +2976,19 @@
         <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45" t="s">
+        <v>133</v>
+      </c>
+      <c r="F45" t="s">
         <v>134</v>
-      </c>
-      <c r="F45" t="s">
-        <v>135</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -3011,7 +2997,7 @@
         <v>6</v>
       </c>
       <c r="J45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
@@ -3019,19 +3005,19 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46" t="s">
+        <v>133</v>
+      </c>
+      <c r="F46" t="s">
         <v>134</v>
-      </c>
-      <c r="F46" t="s">
-        <v>135</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -3040,7 +3026,7 @@
         <v>6</v>
       </c>
       <c r="J46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
@@ -3048,19 +3034,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47" t="s">
+        <v>133</v>
+      </c>
+      <c r="F47" t="s">
         <v>134</v>
-      </c>
-      <c r="F47" t="s">
-        <v>135</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -3069,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="J47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
@@ -3077,20 +3063,20 @@
         <v>39</v>
       </c>
       <c r="B48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F48" t="s">
         <v>164</v>
       </c>
-      <c r="C48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
-      <c r="E48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48" t="s">
-        <v>165</v>
-      </c>
       <c r="G48">
         <v>2</v>
       </c>
@@ -3098,7 +3084,7 @@
         <v>2</v>
       </c>
       <c r="I48" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J48" t="s">
         <v>26</v>
@@ -3112,7 +3098,7 @@
         <v>66</v>
       </c>
       <c r="C49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
@@ -3130,7 +3116,7 @@
         <v>2</v>
       </c>
       <c r="I49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J49" t="s">
         <v>26</v>
@@ -3138,22 +3124,22 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -3164,13 +3150,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" t="s">
         <v>166</v>
       </c>
-      <c r="B51" t="s">
-        <v>167</v>
-      </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
@@ -3190,13 +3176,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>168</v>
+      </c>
+      <c r="B52" t="s">
         <v>169</v>
       </c>
-      <c r="B52" t="s">
-        <v>170</v>
-      </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -3216,13 +3202,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B53" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -3242,22 +3228,22 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B54" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" t="s">
+        <v>106</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" t="s">
+        <v>133</v>
+      </c>
+      <c r="F54" t="s">
         <v>171</v>
-      </c>
-      <c r="C54" t="s">
-        <v>107</v>
-      </c>
-      <c r="D54" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" t="s">
-        <v>134</v>
-      </c>
-      <c r="F54" t="s">
-        <v>172</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -3271,19 +3257,19 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -3292,7 +3278,7 @@
         <v>8</v>
       </c>
       <c r="I55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J55" t="s">
         <v>4</v>
@@ -3306,7 +3292,7 @@
         <v>97</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D56" t="s">
         <v>13</v>
@@ -3324,7 +3310,7 @@
         <v>8</v>
       </c>
       <c r="I56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J56" t="s">
         <v>4</v>
@@ -3335,19 +3321,19 @@
         <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57" t="s">
+        <v>133</v>
+      </c>
+      <c r="F57" t="s">
         <v>134</v>
-      </c>
-      <c r="F57" t="s">
-        <v>135</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -3356,7 +3342,7 @@
         <v>8</v>
       </c>
       <c r="I57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J57" t="s">
         <v>4</v>
@@ -3367,19 +3353,19 @@
         <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -3388,7 +3374,7 @@
         <v>8</v>
       </c>
       <c r="I58" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J58" t="s">
         <v>4</v>
@@ -3399,19 +3385,19 @@
         <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F59" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G59">
         <v>2</v>
@@ -3420,7 +3406,7 @@
         <v>8</v>
       </c>
       <c r="I59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J59" t="s">
         <v>4</v>
@@ -3434,7 +3420,7 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
@@ -3452,7 +3438,7 @@
         <v>8</v>
       </c>
       <c r="I60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J60" t="s">
         <v>4</v>
@@ -3463,19 +3449,19 @@
         <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
       </c>
       <c r="E61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -3484,7 +3470,7 @@
         <v>8</v>
       </c>
       <c r="I61" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J61" t="s">
         <v>4</v>
@@ -3495,19 +3481,19 @@
         <v>19</v>
       </c>
       <c r="B62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G62">
         <v>2</v>
@@ -3516,7 +3502,7 @@
         <v>8</v>
       </c>
       <c r="I62" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J62" t="s">
         <v>4</v>
@@ -3524,19 +3510,19 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
       </c>
       <c r="E63" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
@@ -3550,22 +3536,22 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B64" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
       </c>
       <c r="E64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G64">
         <v>2</v>
@@ -3576,22 +3562,22 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>178</v>
+      </c>
+      <c r="B65" t="s">
         <v>179</v>
       </c>
-      <c r="B65" t="s">
-        <v>180</v>
-      </c>
       <c r="C65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G65">
         <v>2</v>
@@ -3602,22 +3588,22 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B66" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F66" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G66">
         <v>2</v>
@@ -3628,13 +3614,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
+        <v>389</v>
+      </c>
+      <c r="B67" t="s">
         <v>390</v>
       </c>
-      <c r="B67" t="s">
-        <v>391</v>
-      </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
@@ -3660,7 +3646,7 @@
         <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D68" t="s">
         <v>6</v>
@@ -3678,7 +3664,7 @@
         <v>2</v>
       </c>
       <c r="I68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J68" t="s">
         <v>4</v>
@@ -3689,28 +3675,28 @@
         <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C69" t="s">
+        <v>106</v>
+      </c>
+      <c r="D69" t="s">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>133</v>
+      </c>
+      <c r="F69" t="s">
+        <v>134</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+      <c r="I69" t="s">
         <v>107</v>
-      </c>
-      <c r="D69" t="s">
-        <v>5</v>
-      </c>
-      <c r="E69" t="s">
-        <v>134</v>
-      </c>
-      <c r="F69" t="s">
-        <v>135</v>
-      </c>
-      <c r="G69">
-        <v>2</v>
-      </c>
-      <c r="H69">
-        <v>2</v>
-      </c>
-      <c r="I69" t="s">
-        <v>108</v>
       </c>
       <c r="J69" t="s">
         <v>4</v>
@@ -3718,22 +3704,22 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>191</v>
+      </c>
+      <c r="B70" t="s">
         <v>192</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" t="s">
+        <v>5</v>
+      </c>
+      <c r="E70" t="s">
+        <v>109</v>
+      </c>
+      <c r="F70" t="s">
         <v>193</v>
-      </c>
-      <c r="C70" t="s">
-        <v>107</v>
-      </c>
-      <c r="D70" t="s">
-        <v>5</v>
-      </c>
-      <c r="E70" t="s">
-        <v>110</v>
-      </c>
-      <c r="F70" t="s">
-        <v>194</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3750,7 +3736,7 @@
         <v>72</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
@@ -3768,7 +3754,7 @@
         <v>2</v>
       </c>
       <c r="I71" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J71" t="s">
         <v>26</v>
@@ -3782,7 +3768,7 @@
         <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
@@ -3800,7 +3786,7 @@
         <v>2</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J72" t="s">
         <v>26</v>
@@ -3808,22 +3794,22 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>194</v>
+      </c>
+      <c r="B73" t="s">
         <v>195</v>
       </c>
-      <c r="B73" t="s">
-        <v>196</v>
-      </c>
       <c r="C73" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73" t="s">
+        <v>133</v>
+      </c>
+      <c r="F73" t="s">
         <v>134</v>
-      </c>
-      <c r="F73" t="s">
-        <v>135</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3834,22 +3820,22 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>196</v>
+      </c>
+      <c r="B74" t="s">
         <v>197</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
+        <v>106</v>
+      </c>
+      <c r="D74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E74" t="s">
+        <v>133</v>
+      </c>
+      <c r="F74" t="s">
         <v>198</v>
-      </c>
-      <c r="C74" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" t="s">
-        <v>5</v>
-      </c>
-      <c r="E74" t="s">
-        <v>134</v>
-      </c>
-      <c r="F74" t="s">
-        <v>199</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3866,7 +3852,7 @@
         <v>58</v>
       </c>
       <c r="C75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
@@ -3884,7 +3870,7 @@
         <v>2</v>
       </c>
       <c r="I75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J75" t="s">
         <v>4</v>
@@ -3898,7 +3884,7 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
@@ -3916,7 +3902,7 @@
         <v>2</v>
       </c>
       <c r="I76" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J76" t="s">
         <v>4</v>
@@ -3927,10 +3913,10 @@
         <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
@@ -3948,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J77" t="s">
         <v>4</v>
@@ -3956,22 +3942,22 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B78" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78" t="s">
+        <v>133</v>
+      </c>
+      <c r="F78" t="s">
         <v>134</v>
-      </c>
-      <c r="F78" t="s">
-        <v>135</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3982,22 +3968,22 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B79" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F79" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -4008,22 +3994,22 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F80" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -4034,22 +4020,22 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -4060,22 +4046,22 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>200</v>
+      </c>
+      <c r="B82" t="s">
         <v>201</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D82" t="s">
+        <v>5</v>
+      </c>
+      <c r="E82" t="s">
+        <v>133</v>
+      </c>
+      <c r="F82" t="s">
         <v>202</v>
-      </c>
-      <c r="C82" t="s">
-        <v>107</v>
-      </c>
-      <c r="D82" t="s">
-        <v>5</v>
-      </c>
-      <c r="E82" t="s">
-        <v>134</v>
-      </c>
-      <c r="F82" t="s">
-        <v>203</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -4086,22 +4072,22 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
+        <v>206</v>
+      </c>
+      <c r="B83" t="s">
         <v>207</v>
       </c>
-      <c r="B83" t="s">
-        <v>208</v>
-      </c>
       <c r="C83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -4112,22 +4098,22 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B84" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -4144,7 +4130,7 @@
         <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
@@ -4162,7 +4148,7 @@
         <v>2</v>
       </c>
       <c r="I85" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J85" t="s">
         <v>4</v>
@@ -4170,22 +4156,22 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
+        <v>213</v>
+      </c>
+      <c r="B86" t="s">
         <v>214</v>
       </c>
-      <c r="B86" t="s">
-        <v>215</v>
-      </c>
       <c r="C86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -4199,19 +4185,19 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F87" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -4228,7 +4214,7 @@
         <v>62</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
@@ -4251,22 +4237,22 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>216</v>
+      </c>
+      <c r="B89" t="s">
         <v>217</v>
       </c>
-      <c r="B89" t="s">
-        <v>218</v>
-      </c>
       <c r="C89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F89" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -4277,22 +4263,22 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B90" t="s">
+        <v>220</v>
+      </c>
+      <c r="C90" t="s">
+        <v>106</v>
+      </c>
+      <c r="D90" t="s">
+        <v>5</v>
+      </c>
+      <c r="E90" t="s">
+        <v>133</v>
+      </c>
+      <c r="F90" t="s">
         <v>221</v>
-      </c>
-      <c r="C90" t="s">
-        <v>107</v>
-      </c>
-      <c r="D90" t="s">
-        <v>5</v>
-      </c>
-      <c r="E90" t="s">
-        <v>134</v>
-      </c>
-      <c r="F90" t="s">
-        <v>222</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -4303,22 +4289,22 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
+        <v>218</v>
+      </c>
+      <c r="B91" t="s">
         <v>219</v>
       </c>
-      <c r="B91" t="s">
-        <v>220</v>
-      </c>
       <c r="C91" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F91" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -4329,22 +4315,22 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
+        <v>262</v>
+      </c>
+      <c r="B92" t="s">
         <v>263</v>
       </c>
-      <c r="B92" t="s">
-        <v>264</v>
-      </c>
       <c r="C92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
       <c r="E92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -4355,22 +4341,22 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
+        <v>222</v>
+      </c>
+      <c r="B93" t="s">
         <v>223</v>
       </c>
-      <c r="B93" t="s">
-        <v>224</v>
-      </c>
       <c r="C93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F93" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -4381,22 +4367,22 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B94" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F94" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -4407,22 +4393,22 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
+        <v>365</v>
+      </c>
+      <c r="B95" t="s">
         <v>366</v>
       </c>
-      <c r="B95" t="s">
-        <v>367</v>
-      </c>
       <c r="C95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F95" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -4433,22 +4419,22 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
+        <v>228</v>
+      </c>
+      <c r="B96" t="s">
         <v>229</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
+        <v>106</v>
+      </c>
+      <c r="D96" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" t="s">
+        <v>109</v>
+      </c>
+      <c r="F96" t="s">
         <v>230</v>
-      </c>
-      <c r="C96" t="s">
-        <v>107</v>
-      </c>
-      <c r="D96" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" t="s">
-        <v>110</v>
-      </c>
-      <c r="F96" t="s">
-        <v>231</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -4459,22 +4445,22 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B97" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C97" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
       <c r="E97" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F97" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -4485,19 +4471,19 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
+        <v>183</v>
+      </c>
+      <c r="B98" t="s">
         <v>184</v>
       </c>
-      <c r="B98" t="s">
-        <v>185</v>
-      </c>
       <c r="C98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
       <c r="E98" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
@@ -4509,24 +4495,24 @@
         <v>1</v>
       </c>
       <c r="I98" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
+        <v>368</v>
+      </c>
+      <c r="B99" t="s">
         <v>369</v>
       </c>
-      <c r="B99" t="s">
-        <v>370</v>
-      </c>
       <c r="C99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
@@ -4543,19 +4529,19 @@
         <v>33</v>
       </c>
       <c r="B100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -4564,7 +4550,7 @@
         <v>1</v>
       </c>
       <c r="I100" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
@@ -4575,7 +4561,7 @@
         <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
@@ -4595,22 +4581,22 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
+        <v>232</v>
+      </c>
+      <c r="B102" t="s">
         <v>233</v>
       </c>
-      <c r="B102" t="s">
-        <v>234</v>
-      </c>
       <c r="C102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F102" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -4621,22 +4607,22 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B103" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F103" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -4647,22 +4633,22 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B104" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F104" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -4673,22 +4659,22 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
+        <v>236</v>
+      </c>
+      <c r="B105" t="s">
         <v>237</v>
       </c>
-      <c r="B105" t="s">
-        <v>238</v>
-      </c>
       <c r="C105" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F105" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -4705,7 +4691,7 @@
         <v>81</v>
       </c>
       <c r="C106" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D106" t="s">
         <v>6</v>
@@ -4731,7 +4717,7 @@
         <v>75</v>
       </c>
       <c r="C107" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
@@ -4751,22 +4737,22 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
+        <v>185</v>
+      </c>
+      <c r="B108" t="s">
         <v>186</v>
       </c>
-      <c r="B108" t="s">
-        <v>187</v>
-      </c>
       <c r="C108" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F108" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -4777,22 +4763,22 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
+        <v>238</v>
+      </c>
+      <c r="B109" t="s">
         <v>239</v>
       </c>
-      <c r="B109" t="s">
-        <v>240</v>
-      </c>
       <c r="C109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109" t="s">
+        <v>133</v>
+      </c>
+      <c r="F109" t="s">
         <v>134</v>
-      </c>
-      <c r="F109" t="s">
-        <v>135</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -4809,7 +4795,7 @@
         <v>56</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
@@ -4829,22 +4815,22 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C111" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F111" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -4855,22 +4841,22 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
+        <v>240</v>
+      </c>
+      <c r="B112" t="s">
         <v>241</v>
       </c>
-      <c r="B112" t="s">
-        <v>242</v>
-      </c>
       <c r="C112" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112" t="s">
+        <v>133</v>
+      </c>
+      <c r="F112" t="s">
         <v>134</v>
-      </c>
-      <c r="F112" t="s">
-        <v>135</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -4881,22 +4867,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
+        <v>243</v>
+      </c>
+      <c r="B113" t="s">
         <v>244</v>
       </c>
-      <c r="B113" t="s">
-        <v>245</v>
-      </c>
       <c r="C113" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F113" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -4907,22 +4893,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
+        <v>245</v>
+      </c>
+      <c r="B114" t="s">
         <v>246</v>
       </c>
-      <c r="B114" t="s">
-        <v>247</v>
-      </c>
       <c r="C114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F114" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -4933,22 +4919,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B115" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F115" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -4959,22 +4945,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B116" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F116" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -4985,22 +4971,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B117" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C117" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F117" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -5011,22 +4997,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B118" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F118" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -5037,22 +5023,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B119" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F119" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -5063,22 +5049,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B120" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C120" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F120" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -5089,22 +5075,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B121" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C121" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F121" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -5115,22 +5101,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B122" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C122" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F122" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -5141,22 +5127,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B123" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C123" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F123" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -5167,22 +5153,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B124" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C124" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F124" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -5193,22 +5179,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B125" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C125" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F125" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -5219,22 +5205,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
+        <v>225</v>
+      </c>
+      <c r="B126" t="s">
         <v>226</v>
       </c>
-      <c r="B126" t="s">
-        <v>227</v>
-      </c>
       <c r="C126" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F126" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -5245,22 +5231,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B127" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C127" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127" t="s">
+        <v>133</v>
+      </c>
+      <c r="F127" t="s">
         <v>134</v>
-      </c>
-      <c r="F127" t="s">
-        <v>135</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -5271,22 +5257,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
+        <v>255</v>
+      </c>
+      <c r="B128" t="s">
         <v>256</v>
       </c>
-      <c r="B128" t="s">
-        <v>257</v>
-      </c>
       <c r="C128" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F128" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -5297,22 +5283,22 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
+        <v>383</v>
+      </c>
+      <c r="B129" t="s">
         <v>384</v>
       </c>
-      <c r="B129" t="s">
-        <v>385</v>
-      </c>
       <c r="C129" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -5329,7 +5315,7 @@
         <v>76</v>
       </c>
       <c r="C130" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -5347,7 +5333,7 @@
         <v>1</v>
       </c>
       <c r="I130" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J130" t="s">
         <v>24</v>
@@ -5358,28 +5344,28 @@
         <v>18</v>
       </c>
       <c r="B131" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C131" t="s">
+        <v>106</v>
+      </c>
+      <c r="D131" t="s">
+        <v>5</v>
+      </c>
+      <c r="E131" t="s">
+        <v>109</v>
+      </c>
+      <c r="F131" t="s">
+        <v>164</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131" t="s">
         <v>107</v>
-      </c>
-      <c r="D131" t="s">
-        <v>5</v>
-      </c>
-      <c r="E131" t="s">
-        <v>110</v>
-      </c>
-      <c r="F131" t="s">
-        <v>165</v>
-      </c>
-      <c r="G131">
-        <v>1</v>
-      </c>
-      <c r="H131">
-        <v>1</v>
-      </c>
-      <c r="I131" t="s">
-        <v>108</v>
       </c>
       <c r="J131" t="s">
         <v>4</v>
@@ -5387,13 +5373,13 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
+        <v>258</v>
+      </c>
+      <c r="B132" t="s">
         <v>259</v>
       </c>
-      <c r="B132" t="s">
-        <v>260</v>
-      </c>
       <c r="C132" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
@@ -5413,22 +5399,22 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
+        <v>260</v>
+      </c>
+      <c r="B133" t="s">
         <v>261</v>
       </c>
-      <c r="B133" t="s">
-        <v>262</v>
-      </c>
       <c r="C133" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133" t="s">
+        <v>133</v>
+      </c>
+      <c r="F133" t="s">
         <v>134</v>
-      </c>
-      <c r="F133" t="s">
-        <v>135</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -5439,22 +5425,22 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
+        <v>209</v>
+      </c>
+      <c r="B134" t="s">
         <v>210</v>
       </c>
-      <c r="B134" t="s">
-        <v>211</v>
-      </c>
       <c r="C134" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F134" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -5471,7 +5457,7 @@
         <v>96</v>
       </c>
       <c r="C135" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
@@ -5491,22 +5477,22 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
+        <v>265</v>
+      </c>
+      <c r="B136" t="s">
         <v>266</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
+        <v>106</v>
+      </c>
+      <c r="D136" t="s">
+        <v>5</v>
+      </c>
+      <c r="E136" t="s">
+        <v>133</v>
+      </c>
+      <c r="F136" t="s">
         <v>267</v>
-      </c>
-      <c r="C136" t="s">
-        <v>107</v>
-      </c>
-      <c r="D136" t="s">
-        <v>5</v>
-      </c>
-      <c r="E136" t="s">
-        <v>134</v>
-      </c>
-      <c r="F136" t="s">
-        <v>268</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -5517,22 +5503,22 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B137" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C137" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F137" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -5543,23 +5529,23 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
+        <v>272</v>
+      </c>
+      <c r="B138" t="s">
         <v>273</v>
       </c>
-      <c r="B138" t="s">
-        <v>274</v>
-      </c>
       <c r="C138" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138" t="s">
+        <v>109</v>
+      </c>
+      <c r="F138" t="s">
         <v>110</v>
       </c>
-      <c r="F138" t="s">
-        <v>111</v>
-      </c>
       <c r="G138">
         <v>1</v>
       </c>
@@ -5567,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="I138" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J138" t="s">
         <v>26</v>
@@ -5581,7 +5567,7 @@
         <v>70</v>
       </c>
       <c r="C139" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -5599,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="I139" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J139" t="s">
         <v>4</v>
@@ -5607,22 +5593,22 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
+        <v>274</v>
+      </c>
+      <c r="B140" t="s">
         <v>275</v>
       </c>
-      <c r="B140" t="s">
-        <v>276</v>
-      </c>
       <c r="C140" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F140" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -5633,22 +5619,22 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
+        <v>276</v>
+      </c>
+      <c r="B141" t="s">
         <v>277</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
+        <v>106</v>
+      </c>
+      <c r="D141" t="s">
+        <v>5</v>
+      </c>
+      <c r="E141" t="s">
+        <v>133</v>
+      </c>
+      <c r="F141" t="s">
         <v>278</v>
-      </c>
-      <c r="C141" t="s">
-        <v>107</v>
-      </c>
-      <c r="D141" t="s">
-        <v>5</v>
-      </c>
-      <c r="E141" t="s">
-        <v>134</v>
-      </c>
-      <c r="F141" t="s">
-        <v>279</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -5659,22 +5645,22 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
+        <v>279</v>
+      </c>
+      <c r="B142" t="s">
         <v>280</v>
       </c>
-      <c r="B142" t="s">
-        <v>281</v>
-      </c>
       <c r="C142" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F142" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -5691,7 +5677,7 @@
         <v>69</v>
       </c>
       <c r="C143" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D143" t="s">
         <v>13</v>
@@ -5709,7 +5695,7 @@
         <v>1</v>
       </c>
       <c r="I143" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J143" t="s">
         <v>4</v>
@@ -5717,13 +5703,13 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
+        <v>387</v>
+      </c>
+      <c r="B144" t="s">
         <v>388</v>
       </c>
-      <c r="B144" t="s">
-        <v>389</v>
-      </c>
       <c r="C144" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
@@ -5749,7 +5735,7 @@
         <v>80</v>
       </c>
       <c r="C145" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -5769,22 +5755,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
+        <v>312</v>
+      </c>
+      <c r="B146" t="s">
         <v>313</v>
       </c>
-      <c r="B146" t="s">
-        <v>314</v>
-      </c>
       <c r="C146" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F146" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -5795,22 +5781,22 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
+        <v>285</v>
+      </c>
+      <c r="B147" t="s">
         <v>286</v>
       </c>
-      <c r="B147" t="s">
-        <v>287</v>
-      </c>
       <c r="C147" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F147" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -5821,22 +5807,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
+        <v>281</v>
+      </c>
+      <c r="B148" t="s">
         <v>282</v>
       </c>
-      <c r="B148" t="s">
-        <v>283</v>
-      </c>
       <c r="C148" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F148" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -5847,22 +5833,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
+        <v>283</v>
+      </c>
+      <c r="B149" t="s">
         <v>284</v>
       </c>
-      <c r="B149" t="s">
-        <v>285</v>
-      </c>
       <c r="C149" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F149" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -5873,22 +5859,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
+        <v>287</v>
+      </c>
+      <c r="B150" t="s">
         <v>288</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
+        <v>106</v>
+      </c>
+      <c r="D150" t="s">
+        <v>5</v>
+      </c>
+      <c r="E150" t="s">
+        <v>109</v>
+      </c>
+      <c r="F150" t="s">
         <v>289</v>
-      </c>
-      <c r="C150" t="s">
-        <v>107</v>
-      </c>
-      <c r="D150" t="s">
-        <v>5</v>
-      </c>
-      <c r="E150" t="s">
-        <v>110</v>
-      </c>
-      <c r="F150" t="s">
-        <v>290</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -5899,22 +5885,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B151" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C151" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F151" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -5925,22 +5911,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
+        <v>291</v>
+      </c>
+      <c r="B152" t="s">
         <v>292</v>
       </c>
-      <c r="B152" t="s">
-        <v>293</v>
-      </c>
       <c r="C152" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152" t="s">
+        <v>133</v>
+      </c>
+      <c r="F152" t="s">
         <v>134</v>
-      </c>
-      <c r="F152" t="s">
-        <v>135</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -5951,22 +5937,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B153" t="s">
+        <v>293</v>
+      </c>
+      <c r="C153" t="s">
+        <v>106</v>
+      </c>
+      <c r="D153" t="s">
+        <v>5</v>
+      </c>
+      <c r="E153" t="s">
+        <v>133</v>
+      </c>
+      <c r="F153" t="s">
         <v>294</v>
-      </c>
-      <c r="C153" t="s">
-        <v>107</v>
-      </c>
-      <c r="D153" t="s">
-        <v>5</v>
-      </c>
-      <c r="E153" t="s">
-        <v>134</v>
-      </c>
-      <c r="F153" t="s">
-        <v>295</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -5977,22 +5963,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
+        <v>295</v>
+      </c>
+      <c r="B154" t="s">
         <v>296</v>
       </c>
-      <c r="B154" t="s">
-        <v>297</v>
-      </c>
       <c r="C154" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F154" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -6003,22 +5989,22 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B155" t="s">
+        <v>297</v>
+      </c>
+      <c r="C155" t="s">
+        <v>106</v>
+      </c>
+      <c r="D155" t="s">
+        <v>5</v>
+      </c>
+      <c r="E155" t="s">
+        <v>109</v>
+      </c>
+      <c r="F155" t="s">
         <v>298</v>
-      </c>
-      <c r="C155" t="s">
-        <v>107</v>
-      </c>
-      <c r="D155" t="s">
-        <v>5</v>
-      </c>
-      <c r="E155" t="s">
-        <v>110</v>
-      </c>
-      <c r="F155" t="s">
-        <v>299</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -6029,22 +6015,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B156" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C156" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F156" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -6055,22 +6041,22 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B157" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C157" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157" t="s">
+        <v>133</v>
+      </c>
+      <c r="F157" t="s">
         <v>134</v>
-      </c>
-      <c r="F157" t="s">
-        <v>135</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -6081,22 +6067,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
+        <v>299</v>
+      </c>
+      <c r="B158" t="s">
         <v>300</v>
       </c>
-      <c r="B158" t="s">
-        <v>301</v>
-      </c>
       <c r="C158" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158" t="s">
+        <v>133</v>
+      </c>
+      <c r="F158" t="s">
         <v>134</v>
-      </c>
-      <c r="F158" t="s">
-        <v>135</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -6107,22 +6093,22 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B159" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C159" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F159" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -6133,22 +6119,22 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B160" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C160" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160" t="s">
+        <v>133</v>
+      </c>
+      <c r="F160" t="s">
         <v>134</v>
-      </c>
-      <c r="F160" t="s">
-        <v>135</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -6162,10 +6148,10 @@
         <v>49</v>
       </c>
       <c r="B161" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C161" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -6183,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="I161" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J161" t="s">
         <v>24</v>
@@ -6191,22 +6177,22 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B162" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C162" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F162" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -6217,22 +6203,22 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B163" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C163" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F163" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -6243,22 +6229,22 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
+        <v>306</v>
+      </c>
+      <c r="B164" t="s">
         <v>307</v>
       </c>
-      <c r="B164" t="s">
-        <v>308</v>
-      </c>
       <c r="C164" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F164" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -6269,22 +6255,22 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B165" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C165" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F165" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -6298,19 +6284,19 @@
         <v>29</v>
       </c>
       <c r="B166" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C166" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F166" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -6321,22 +6307,22 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
+        <v>328</v>
+      </c>
+      <c r="B167" t="s">
         <v>329</v>
       </c>
-      <c r="B167" t="s">
-        <v>330</v>
-      </c>
       <c r="C167" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F167" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -6347,23 +6333,23 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
+        <v>314</v>
+      </c>
+      <c r="B168" t="s">
         <v>315</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
+        <v>106</v>
+      </c>
+      <c r="D168" t="s">
+        <v>5</v>
+      </c>
+      <c r="E168" t="s">
+        <v>117</v>
+      </c>
+      <c r="F168" t="s">
         <v>316</v>
       </c>
-      <c r="C168" t="s">
-        <v>107</v>
-      </c>
-      <c r="D168" t="s">
-        <v>5</v>
-      </c>
-      <c r="E168" t="s">
-        <v>118</v>
-      </c>
-      <c r="F168" t="s">
-        <v>317</v>
-      </c>
       <c r="G168">
         <v>1</v>
       </c>
@@ -6371,7 +6357,7 @@
         <v>1</v>
       </c>
       <c r="I168" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J168" t="s">
         <v>4</v>
@@ -6379,22 +6365,22 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
+        <v>317</v>
+      </c>
+      <c r="B169" t="s">
         <v>318</v>
       </c>
-      <c r="B169" t="s">
-        <v>319</v>
-      </c>
       <c r="C169" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F169" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -6405,22 +6391,22 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
+        <v>319</v>
+      </c>
+      <c r="B170" t="s">
         <v>320</v>
       </c>
-      <c r="B170" t="s">
-        <v>321</v>
-      </c>
       <c r="C170" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F170" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -6431,22 +6417,22 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B171" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C171" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="E171" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F171" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -6460,10 +6446,10 @@
         <v>7</v>
       </c>
       <c r="B172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C172" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
@@ -6481,7 +6467,7 @@
         <v>2</v>
       </c>
       <c r="I172" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J172" t="s">
         <v>4</v>
@@ -6495,7 +6481,7 @@
         <v>400</v>
       </c>
       <c r="C173" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D173" t="s">
         <v>13</v>
@@ -6513,7 +6499,7 @@
         <v>2</v>
       </c>
       <c r="I173" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J173" t="s">
         <v>4</v>
@@ -6521,22 +6507,22 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
+        <v>322</v>
+      </c>
+      <c r="B174" t="s">
         <v>323</v>
       </c>
-      <c r="B174" t="s">
-        <v>324</v>
-      </c>
       <c r="C174" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F174" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -6547,22 +6533,22 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
+        <v>324</v>
+      </c>
+      <c r="B175" t="s">
         <v>325</v>
       </c>
-      <c r="B175" t="s">
-        <v>326</v>
-      </c>
       <c r="C175" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F175" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -6573,13 +6559,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
+        <v>326</v>
+      </c>
+      <c r="B176" t="s">
         <v>327</v>
       </c>
-      <c r="B176" t="s">
-        <v>328</v>
-      </c>
       <c r="C176" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -6602,10 +6588,10 @@
         <v>42</v>
       </c>
       <c r="B177" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C177" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -6623,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="I177" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J177" t="s">
         <v>26</v>
@@ -6637,7 +6623,7 @@
         <v>83</v>
       </c>
       <c r="C178" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
@@ -6655,10 +6641,10 @@
         <v>1</v>
       </c>
       <c r="I178" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J178" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.35">
@@ -6666,10 +6652,10 @@
         <v>73</v>
       </c>
       <c r="B179" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C179" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
@@ -6687,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="I179" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J179" t="s">
         <v>24</v>
@@ -6695,22 +6681,22 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
+        <v>332</v>
+      </c>
+      <c r="B180" t="s">
         <v>333</v>
       </c>
-      <c r="B180" t="s">
-        <v>334</v>
-      </c>
       <c r="C180" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
       <c r="E180" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F180" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G180">
         <v>1</v>
@@ -6721,22 +6707,22 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B181" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C181" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
       </c>
       <c r="E181" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F181" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -6747,22 +6733,22 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B182" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C182" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
       <c r="E182" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F182" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G182">
         <v>1</v>
@@ -6773,22 +6759,22 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B183" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C183" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
       <c r="E183" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F183" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G183">
         <v>1</v>
@@ -6799,22 +6785,22 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B184" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C184" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
       </c>
       <c r="E184" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F184" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -6825,22 +6811,22 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B185" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C185" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
       </c>
       <c r="E185" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F185" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -6851,22 +6837,22 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B186" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C186" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
       </c>
       <c r="E186" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F186" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -6877,22 +6863,22 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B187" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C187" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
       </c>
       <c r="E187" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F187" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -6903,22 +6889,22 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B188" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C188" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
       </c>
       <c r="E188" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F188" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -6929,22 +6915,22 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B189" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C189" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
       <c r="E189" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F189" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -6955,22 +6941,22 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B190" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C190" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
       </c>
       <c r="E190" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F190" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -6981,22 +6967,22 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
+        <v>343</v>
+      </c>
+      <c r="B191" t="s">
         <v>344</v>
       </c>
-      <c r="B191" t="s">
-        <v>345</v>
-      </c>
       <c r="C191" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
       </c>
       <c r="E191" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F191" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G191">
         <v>1</v>
@@ -7007,22 +6993,22 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
+        <v>345</v>
+      </c>
+      <c r="B192" t="s">
         <v>346</v>
       </c>
-      <c r="B192" t="s">
-        <v>347</v>
-      </c>
       <c r="C192" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
       </c>
       <c r="E192" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F192" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G192">
         <v>1</v>
@@ -7033,22 +7019,22 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
+        <v>347</v>
+      </c>
+      <c r="B193" t="s">
         <v>348</v>
       </c>
-      <c r="B193" t="s">
-        <v>349</v>
-      </c>
       <c r="C193" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D193" t="s">
         <v>5</v>
       </c>
       <c r="E193" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F193" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G193">
         <v>1</v>
@@ -7062,10 +7048,10 @@
         <v>23</v>
       </c>
       <c r="B194" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C194" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D194" t="s">
         <v>5</v>
@@ -7083,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="I194" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J194" t="s">
         <v>26</v>
@@ -7091,22 +7077,22 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
+        <v>351</v>
+      </c>
+      <c r="B195" t="s">
         <v>352</v>
       </c>
-      <c r="B195" t="s">
-        <v>353</v>
-      </c>
       <c r="C195" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D195" t="s">
         <v>5</v>
       </c>
       <c r="E195" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F195" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G195">
         <v>1</v>
@@ -7117,22 +7103,22 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B196" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C196" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D196" t="s">
         <v>5</v>
       </c>
       <c r="E196" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F196" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -7143,51 +7129,51 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
+        <v>354</v>
+      </c>
+      <c r="B197" t="s">
         <v>355</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
+        <v>106</v>
+      </c>
+      <c r="D197" t="s">
+        <v>5</v>
+      </c>
+      <c r="E197" t="s">
+        <v>109</v>
+      </c>
+      <c r="F197" t="s">
+        <v>164</v>
+      </c>
+      <c r="G197">
+        <v>1</v>
+      </c>
+      <c r="H197">
+        <v>1</v>
+      </c>
+      <c r="I197" t="s">
         <v>356</v>
-      </c>
-      <c r="C197" t="s">
-        <v>107</v>
-      </c>
-      <c r="D197" t="s">
-        <v>5</v>
-      </c>
-      <c r="E197" t="s">
-        <v>110</v>
-      </c>
-      <c r="F197" t="s">
-        <v>165</v>
-      </c>
-      <c r="G197">
-        <v>1</v>
-      </c>
-      <c r="H197">
-        <v>1</v>
-      </c>
-      <c r="I197" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
+        <v>357</v>
+      </c>
+      <c r="B198" t="s">
         <v>358</v>
       </c>
-      <c r="B198" t="s">
-        <v>359</v>
-      </c>
       <c r="C198" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D198" t="s">
         <v>5</v>
       </c>
       <c r="E198" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F198" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -7198,19 +7184,19 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
+        <v>359</v>
+      </c>
+      <c r="B199" t="s">
         <v>360</v>
       </c>
-      <c r="B199" t="s">
-        <v>361</v>
-      </c>
       <c r="C199" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D199" t="s">
         <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F199" t="s">
         <v>12</v>
@@ -7224,22 +7210,22 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
+        <v>361</v>
+      </c>
+      <c r="B200" t="s">
         <v>362</v>
       </c>
-      <c r="B200" t="s">
-        <v>363</v>
-      </c>
       <c r="C200" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D200" t="s">
         <v>5</v>
       </c>
       <c r="E200" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F200" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G200">
         <v>1</v>
@@ -7250,22 +7236,22 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
+        <v>363</v>
+      </c>
+      <c r="B201" t="s">
         <v>364</v>
       </c>
-      <c r="B201" t="s">
-        <v>365</v>
-      </c>
       <c r="C201" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D201" t="s">
         <v>5</v>
       </c>
       <c r="E201" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F201" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G201">
         <v>1</v>
@@ -7274,7 +7260,7 @@
         <v>1</v>
       </c>
       <c r="I201" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J201" t="s">
         <v>26</v>
@@ -7282,22 +7268,22 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B202" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C202" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D202" t="s">
         <v>5</v>
       </c>
       <c r="E202" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F202" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G202">
         <v>1</v>
@@ -7308,22 +7294,22 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
+        <v>189</v>
+      </c>
+      <c r="B203" t="s">
         <v>190</v>
       </c>
-      <c r="B203" t="s">
-        <v>191</v>
-      </c>
       <c r="C203" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D203" t="s">
         <v>5</v>
       </c>
       <c r="E203" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F203" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G203">
         <v>1</v>
@@ -7334,22 +7320,22 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B204" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C204" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D204" t="s">
         <v>5</v>
       </c>
       <c r="E204" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F204" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -7360,22 +7346,22 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B205" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C205" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D205" t="s">
         <v>5</v>
       </c>
       <c r="E205" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F205" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G205">
         <v>1</v>
@@ -7386,13 +7372,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
+        <v>187</v>
+      </c>
+      <c r="B206" t="s">
         <v>188</v>
       </c>
-      <c r="B206" t="s">
-        <v>189</v>
-      </c>
       <c r="C206" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D206" t="s">
         <v>5</v>
@@ -7412,22 +7398,22 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
+        <v>370</v>
+      </c>
+      <c r="B207" t="s">
         <v>371</v>
       </c>
-      <c r="B207" t="s">
-        <v>372</v>
-      </c>
       <c r="C207" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D207" t="s">
         <v>5</v>
       </c>
       <c r="E207" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F207" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G207">
         <v>1</v>
@@ -7438,22 +7424,22 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B208" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C208" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D208" t="s">
         <v>5</v>
       </c>
       <c r="E208" t="s">
+        <v>133</v>
+      </c>
+      <c r="F208" t="s">
         <v>134</v>
-      </c>
-      <c r="F208" t="s">
-        <v>135</v>
       </c>
       <c r="G208">
         <v>1</v>
@@ -7464,22 +7450,22 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
+        <v>372</v>
+      </c>
+      <c r="B209" t="s">
         <v>373</v>
       </c>
-      <c r="B209" t="s">
-        <v>374</v>
-      </c>
       <c r="C209" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D209" t="s">
         <v>5</v>
       </c>
       <c r="E209" t="s">
+        <v>133</v>
+      </c>
+      <c r="F209" t="s">
         <v>134</v>
-      </c>
-      <c r="F209" t="s">
-        <v>135</v>
       </c>
       <c r="G209">
         <v>1</v>
@@ -7490,22 +7476,22 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
+        <v>269</v>
+      </c>
+      <c r="B210" t="s">
         <v>270</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
+        <v>106</v>
+      </c>
+      <c r="D210" t="s">
+        <v>5</v>
+      </c>
+      <c r="E210" t="s">
+        <v>133</v>
+      </c>
+      <c r="F210" t="s">
         <v>271</v>
-      </c>
-      <c r="C210" t="s">
-        <v>107</v>
-      </c>
-      <c r="D210" t="s">
-        <v>5</v>
-      </c>
-      <c r="E210" t="s">
-        <v>134</v>
-      </c>
-      <c r="F210" t="s">
-        <v>272</v>
       </c>
       <c r="G210">
         <v>1</v>
@@ -7516,22 +7502,22 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
+        <v>375</v>
+      </c>
+      <c r="B211" t="s">
         <v>376</v>
       </c>
-      <c r="B211" t="s">
-        <v>377</v>
-      </c>
       <c r="C211" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D211" t="s">
         <v>5</v>
       </c>
       <c r="E211" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F211" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -7542,22 +7528,22 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
+        <v>377</v>
+      </c>
+      <c r="B212" t="s">
         <v>378</v>
       </c>
-      <c r="B212" t="s">
-        <v>379</v>
-      </c>
       <c r="C212" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D212" t="s">
         <v>5</v>
       </c>
       <c r="E212" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F212" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G212">
         <v>1</v>
@@ -7568,22 +7554,22 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
+        <v>379</v>
+      </c>
+      <c r="B213" t="s">
         <v>380</v>
       </c>
-      <c r="B213" t="s">
-        <v>381</v>
-      </c>
       <c r="C213" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D213" t="s">
         <v>5</v>
       </c>
       <c r="E213" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F213" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G213">
         <v>1</v>
@@ -7597,20 +7583,20 @@
         <v>43</v>
       </c>
       <c r="B214" t="s">
+        <v>381</v>
+      </c>
+      <c r="C214" t="s">
+        <v>106</v>
+      </c>
+      <c r="D214" t="s">
+        <v>5</v>
+      </c>
+      <c r="E214" t="s">
+        <v>133</v>
+      </c>
+      <c r="F214" t="s">
         <v>382</v>
       </c>
-      <c r="C214" t="s">
-        <v>107</v>
-      </c>
-      <c r="D214" t="s">
-        <v>5</v>
-      </c>
-      <c r="E214" t="s">
-        <v>134</v>
-      </c>
-      <c r="F214" t="s">
-        <v>383</v>
-      </c>
       <c r="G214">
         <v>1</v>
       </c>
@@ -7618,7 +7604,7 @@
         <v>1</v>
       </c>
       <c r="I214" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J214" t="s">
         <v>4</v>
@@ -7632,7 +7618,7 @@
         <v>89</v>
       </c>
       <c r="C215" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D215" t="s">
         <v>5</v>
@@ -7658,7 +7644,7 @@
         <v>91</v>
       </c>
       <c r="C216" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D216" t="s">
         <v>5</v>
@@ -7676,14 +7662,14 @@
         <v>1</v>
       </c>
       <c r="I216" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J216" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K216" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J216" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Clientes_25-26_frentes_padronizado.xlsx
+++ b/Clientes_25-26_frentes_padronizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas moreira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAADF3C-5D61-4901-A60D-4C685AE0ADF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CD7219-AFF0-447B-AD66-67075051ED39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -340,6 +340,9 @@
     <t>PepsiCo - PepsiCo First Gen 2025 - Ciclo 25/26</t>
   </si>
   <si>
+    <t>Empresa relacionada - Nomes</t>
+  </si>
+  <si>
     <t>Nome</t>
   </si>
   <si>
@@ -1241,9 +1244,6 @@
   </si>
   <si>
     <t>Sebrae - Links Facet5 Fevereiro 2026</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Programa de Estágio Bracell Ciclo 26/27</t>
@@ -1305,12 +1305,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1630,32 +1627,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>399</v>
+      <c r="A1" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>0</v>
@@ -1666,19 +1663,19 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1687,7 +1684,7 @@
         <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J2" t="s">
         <v>4</v>
@@ -1698,19 +1695,19 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1719,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
@@ -1730,19 +1727,19 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1751,7 +1748,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
@@ -1762,19 +1759,19 @@
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1783,7 +1780,7 @@
         <v>8</v>
       </c>
       <c r="I5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
@@ -1794,19 +1791,19 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1815,7 +1812,7 @@
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
@@ -1826,19 +1823,19 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1847,7 +1844,7 @@
         <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
@@ -1861,7 +1858,7 @@
         <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -1879,7 +1876,7 @@
         <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
@@ -1893,7 +1890,7 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1911,7 +1908,7 @@
         <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
@@ -1925,7 +1922,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1943,10 +1940,10 @@
         <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -1954,19 +1951,19 @@
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -1975,10 +1972,10 @@
         <v>4</v>
       </c>
       <c r="I11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -1986,19 +1983,19 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -2007,10 +2004,10 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -2021,7 +2018,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -2039,10 +2036,10 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -2053,7 +2050,7 @@
         <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -2071,7 +2068,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
@@ -2082,19 +2079,19 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -2103,7 +2100,7 @@
         <v>3</v>
       </c>
       <c r="I15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
@@ -2114,19 +2111,19 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -2135,7 +2132,7 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
@@ -2146,10 +2143,10 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
@@ -2167,7 +2164,7 @@
         <v>3</v>
       </c>
       <c r="I17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J17" t="s">
         <v>4</v>
@@ -2181,7 +2178,7 @@
         <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
@@ -2199,7 +2196,7 @@
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J18" t="s">
         <v>4</v>
@@ -2210,19 +2207,19 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -2231,7 +2228,7 @@
         <v>4</v>
       </c>
       <c r="I19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J19" t="s">
         <v>4</v>
@@ -2242,19 +2239,19 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G20">
         <v>3</v>
@@ -2263,7 +2260,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J20" t="s">
         <v>4</v>
@@ -2271,22 +2268,22 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -2297,22 +2294,22 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -2326,19 +2323,19 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2352,16 +2349,16 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -2378,19 +2375,19 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -2404,19 +2401,19 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -2430,10 +2427,10 @@
         <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -2451,10 +2448,10 @@
         <v>2</v>
       </c>
       <c r="I27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
@@ -2462,31 +2459,31 @@
         <v>67</v>
       </c>
       <c r="B28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28" t="s">
         <v>143</v>
       </c>
-      <c r="C28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28" t="s">
-        <v>109</v>
-      </c>
-      <c r="F28" t="s">
-        <v>114</v>
-      </c>
-      <c r="G28">
-        <v>2</v>
-      </c>
-      <c r="H28">
-        <v>2</v>
-      </c>
-      <c r="I28" t="s">
-        <v>142</v>
-      </c>
       <c r="J28" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
@@ -2497,7 +2494,7 @@
         <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
@@ -2515,7 +2512,7 @@
         <v>3</v>
       </c>
       <c r="I29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
@@ -2523,19 +2520,19 @@
         <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -2544,7 +2541,7 @@
         <v>3</v>
       </c>
       <c r="I30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
@@ -2552,19 +2549,19 @@
         <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2573,7 +2570,7 @@
         <v>3</v>
       </c>
       <c r="I31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
@@ -2584,7 +2581,7 @@
         <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -2610,19 +2607,19 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2639,19 +2636,19 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -2660,7 +2657,7 @@
         <v>4</v>
       </c>
       <c r="I34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J34" t="s">
         <v>26</v>
@@ -2674,7 +2671,7 @@
         <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
@@ -2692,7 +2689,7 @@
         <v>4</v>
       </c>
       <c r="I35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J35" t="s">
         <v>26</v>
@@ -2703,19 +2700,19 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2724,7 +2721,7 @@
         <v>4</v>
       </c>
       <c r="I36" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J36" t="s">
         <v>26</v>
@@ -2735,19 +2732,19 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2756,7 +2753,7 @@
         <v>4</v>
       </c>
       <c r="I37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J37" t="s">
         <v>26</v>
@@ -2767,10 +2764,10 @@
         <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
@@ -2788,7 +2785,7 @@
         <v>2</v>
       </c>
       <c r="I38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J38" t="s">
         <v>4</v>
@@ -2799,28 +2796,28 @@
         <v>57</v>
       </c>
       <c r="B39" t="s">
+        <v>157</v>
+      </c>
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" t="s">
+        <v>134</v>
+      </c>
+      <c r="F39" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39" t="s">
         <v>156</v>
-      </c>
-      <c r="C39" t="s">
-        <v>106</v>
-      </c>
-      <c r="D39" t="s">
-        <v>5</v>
-      </c>
-      <c r="E39" t="s">
-        <v>133</v>
-      </c>
-      <c r="F39" t="s">
-        <v>139</v>
-      </c>
-      <c r="G39">
-        <v>2</v>
-      </c>
-      <c r="H39">
-        <v>2</v>
-      </c>
-      <c r="I39" t="s">
-        <v>155</v>
       </c>
       <c r="J39" t="s">
         <v>4</v>
@@ -2831,28 +2828,28 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" t="s">
+        <v>115</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+      <c r="I40" t="s">
         <v>158</v>
-      </c>
-      <c r="C40" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" t="s">
-        <v>5</v>
-      </c>
-      <c r="E40" t="s">
-        <v>109</v>
-      </c>
-      <c r="F40" t="s">
-        <v>114</v>
-      </c>
-      <c r="G40">
-        <v>2</v>
-      </c>
-      <c r="H40">
-        <v>2</v>
-      </c>
-      <c r="I40" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
@@ -2863,7 +2860,7 @@
         <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -2881,7 +2878,7 @@
         <v>2</v>
       </c>
       <c r="I41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
@@ -2892,7 +2889,7 @@
         <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -2910,7 +2907,7 @@
         <v>6</v>
       </c>
       <c r="J42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
@@ -2921,7 +2918,7 @@
         <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -2939,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="J43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
@@ -2947,19 +2944,19 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F44" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2968,7 +2965,7 @@
         <v>6</v>
       </c>
       <c r="J44" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
@@ -2976,19 +2973,19 @@
         <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -2997,7 +2994,7 @@
         <v>6</v>
       </c>
       <c r="J45" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
@@ -3005,19 +3002,19 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -3026,7 +3023,7 @@
         <v>6</v>
       </c>
       <c r="J46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
@@ -3034,19 +3031,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -3055,7 +3052,7 @@
         <v>6</v>
       </c>
       <c r="J47" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
@@ -3063,19 +3060,19 @@
         <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -3084,7 +3081,7 @@
         <v>2</v>
       </c>
       <c r="I48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J48" t="s">
         <v>26</v>
@@ -3098,7 +3095,7 @@
         <v>66</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
@@ -3116,7 +3113,7 @@
         <v>2</v>
       </c>
       <c r="I49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J49" t="s">
         <v>26</v>
@@ -3124,22 +3121,22 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -3150,13 +3147,13 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
@@ -3176,13 +3173,13 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C52" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -3202,13 +3199,13 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B53" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -3228,22 +3225,22 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -3257,19 +3254,19 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
       <c r="E55" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -3278,7 +3275,7 @@
         <v>8</v>
       </c>
       <c r="I55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J55" t="s">
         <v>4</v>
@@ -3292,7 +3289,7 @@
         <v>97</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D56" t="s">
         <v>13</v>
@@ -3310,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="I56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J56" t="s">
         <v>4</v>
@@ -3321,19 +3318,19 @@
         <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F57" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -3342,7 +3339,7 @@
         <v>8</v>
       </c>
       <c r="I57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J57" t="s">
         <v>4</v>
@@ -3353,19 +3350,19 @@
         <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F58" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -3374,7 +3371,7 @@
         <v>8</v>
       </c>
       <c r="I58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J58" t="s">
         <v>4</v>
@@ -3385,19 +3382,19 @@
         <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F59" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G59">
         <v>2</v>
@@ -3406,7 +3403,7 @@
         <v>8</v>
       </c>
       <c r="I59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J59" t="s">
         <v>4</v>
@@ -3420,7 +3417,7 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
@@ -3438,7 +3435,7 @@
         <v>8</v>
       </c>
       <c r="I60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J60" t="s">
         <v>4</v>
@@ -3449,19 +3446,19 @@
         <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
       </c>
       <c r="E61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F61" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -3470,7 +3467,7 @@
         <v>8</v>
       </c>
       <c r="I61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J61" t="s">
         <v>4</v>
@@ -3481,19 +3478,19 @@
         <v>19</v>
       </c>
       <c r="B62" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F62" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G62">
         <v>2</v>
@@ -3502,7 +3499,7 @@
         <v>8</v>
       </c>
       <c r="I62" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J62" t="s">
         <v>4</v>
@@ -3510,19 +3507,19 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B63" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C63" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
       </c>
       <c r="E63" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
@@ -3536,22 +3533,22 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C64" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
       </c>
       <c r="E64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G64">
         <v>2</v>
@@ -3562,22 +3559,22 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B65" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F65" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G65">
         <v>2</v>
@@ -3588,22 +3585,22 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B66" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C66" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F66" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G66">
         <v>2</v>
@@ -3614,13 +3611,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B67" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C67" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
@@ -3646,7 +3643,7 @@
         <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D68" t="s">
         <v>6</v>
@@ -3664,7 +3661,7 @@
         <v>2</v>
       </c>
       <c r="I68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J68" t="s">
         <v>4</v>
@@ -3675,19 +3672,19 @@
         <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C69" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F69" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G69">
         <v>2</v>
@@ -3696,7 +3693,7 @@
         <v>2</v>
       </c>
       <c r="I69" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J69" t="s">
         <v>4</v>
@@ -3704,22 +3701,22 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B70" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="E70" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F70" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3736,7 +3733,7 @@
         <v>72</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
@@ -3754,7 +3751,7 @@
         <v>2</v>
       </c>
       <c r="I71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J71" t="s">
         <v>26</v>
@@ -3768,7 +3765,7 @@
         <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
@@ -3786,7 +3783,7 @@
         <v>2</v>
       </c>
       <c r="I72" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J72" t="s">
         <v>26</v>
@@ -3794,22 +3791,22 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B73" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
       <c r="E73" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F73" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3820,22 +3817,22 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B74" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C74" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F74" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3852,7 +3849,7 @@
         <v>58</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
@@ -3870,7 +3867,7 @@
         <v>2</v>
       </c>
       <c r="I75" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J75" t="s">
         <v>4</v>
@@ -3884,7 +3881,7 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
@@ -3902,7 +3899,7 @@
         <v>2</v>
       </c>
       <c r="I76" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J76" t="s">
         <v>4</v>
@@ -3913,10 +3910,10 @@
         <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C77" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
@@ -3934,7 +3931,7 @@
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J77" t="s">
         <v>4</v>
@@ -3942,22 +3939,22 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B78" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F78" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3968,22 +3965,22 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C79" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F79" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3994,22 +3991,22 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B80" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C80" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
       <c r="E80" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -4020,22 +4017,22 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C81" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F81" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -4046,22 +4043,22 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B82" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -4072,22 +4069,22 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B83" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
       <c r="E83" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -4098,22 +4095,22 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B84" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F84" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -4130,7 +4127,7 @@
         <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
@@ -4148,7 +4145,7 @@
         <v>2</v>
       </c>
       <c r="I85" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J85" t="s">
         <v>4</v>
@@ -4156,22 +4153,22 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B86" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C86" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
       <c r="E86" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F86" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -4185,19 +4182,19 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C87" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -4214,7 +4211,7 @@
         <v>62</v>
       </c>
       <c r="C88" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
@@ -4237,22 +4234,22 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B89" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C89" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F89" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -4263,22 +4260,22 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C90" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F90" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -4289,22 +4286,22 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C91" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="E91" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F91" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -4315,22 +4312,22 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C92" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
       <c r="E92" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -4341,22 +4338,22 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B93" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C93" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -4367,22 +4364,22 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B94" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C94" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="E94" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F94" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -4393,22 +4390,22 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B95" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C95" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
       <c r="E95" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F95" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -4419,22 +4416,22 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B96" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C96" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F96" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -4445,22 +4442,22 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B97" t="s">
+        <v>232</v>
+      </c>
+      <c r="C97" t="s">
+        <v>107</v>
+      </c>
+      <c r="D97" t="s">
+        <v>5</v>
+      </c>
+      <c r="E97" t="s">
+        <v>110</v>
+      </c>
+      <c r="F97" t="s">
         <v>231</v>
-      </c>
-      <c r="C97" t="s">
-        <v>106</v>
-      </c>
-      <c r="D97" t="s">
-        <v>5</v>
-      </c>
-      <c r="E97" t="s">
-        <v>109</v>
-      </c>
-      <c r="F97" t="s">
-        <v>230</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -4471,19 +4468,19 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B98" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C98" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
       <c r="E98" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
@@ -4495,24 +4492,24 @@
         <v>1</v>
       </c>
       <c r="I98" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B99" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C99" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
@@ -4529,19 +4526,19 @@
         <v>33</v>
       </c>
       <c r="B100" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C100" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F100" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -4550,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="I100" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
@@ -4561,7 +4558,7 @@
         <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
@@ -4581,22 +4578,22 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B102" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C102" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F102" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -4607,22 +4604,22 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B103" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C103" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="E103" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F103" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -4633,22 +4630,22 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B104" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C104" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="E104" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F104" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -4659,22 +4656,22 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B105" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C105" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F105" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -4691,7 +4688,7 @@
         <v>81</v>
       </c>
       <c r="C106" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D106" t="s">
         <v>6</v>
@@ -4717,7 +4714,7 @@
         <v>75</v>
       </c>
       <c r="C107" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
@@ -4737,22 +4734,22 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B108" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C108" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F108" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -4763,22 +4760,22 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B109" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="E109" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F109" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -4795,7 +4792,7 @@
         <v>56</v>
       </c>
       <c r="C110" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
@@ -4815,22 +4812,22 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B111" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C111" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F111" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -4841,22 +4838,22 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B112" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C112" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
       <c r="E112" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F112" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -4867,22 +4864,22 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B113" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C113" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F113" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -4893,22 +4890,22 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B114" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F114" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -4919,22 +4916,22 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B115" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C115" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
       </c>
       <c r="E115" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F115" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -4945,22 +4942,22 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B116" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C116" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F116" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -4971,22 +4968,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B117" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F117" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -4997,22 +4994,22 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B118" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C118" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
       </c>
       <c r="E118" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F118" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -5023,22 +5020,22 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B119" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C119" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
       </c>
       <c r="E119" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F119" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -5049,22 +5046,22 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B120" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C120" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F120" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -5075,22 +5072,22 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B121" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C121" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
       </c>
       <c r="E121" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F121" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -5101,22 +5098,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B122" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C122" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
       </c>
       <c r="E122" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F122" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -5127,22 +5124,22 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B123" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C123" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F123" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -5153,22 +5150,22 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B124" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C124" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
       </c>
       <c r="E124" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F124" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -5179,22 +5176,22 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B125" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C125" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F125" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -5205,22 +5202,22 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B126" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C126" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F126" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -5231,22 +5228,22 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B127" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C127" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="E127" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F127" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -5257,22 +5254,22 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C128" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F128" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -5283,22 +5280,22 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B129" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C129" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F129" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -5315,7 +5312,7 @@
         <v>76</v>
       </c>
       <c r="C130" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -5333,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="I130" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J130" t="s">
         <v>24</v>
@@ -5344,19 +5341,19 @@
         <v>18</v>
       </c>
       <c r="B131" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C131" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F131" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -5365,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="I131" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J131" t="s">
         <v>4</v>
@@ -5373,13 +5370,13 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B132" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C132" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
@@ -5399,22 +5396,22 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B133" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C133" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="E133" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F133" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -5425,22 +5422,22 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B134" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C134" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
       <c r="E134" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F134" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -5457,7 +5454,7 @@
         <v>96</v>
       </c>
       <c r="C135" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
@@ -5477,22 +5474,22 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B136" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C136" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D136" t="s">
         <v>5</v>
       </c>
       <c r="E136" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F136" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -5503,22 +5500,22 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B137" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C137" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
       </c>
       <c r="E137" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F137" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -5529,22 +5526,22 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B138" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C138" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
       <c r="E138" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F138" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -5553,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="I138" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J138" t="s">
         <v>26</v>
@@ -5567,7 +5564,7 @@
         <v>70</v>
       </c>
       <c r="C139" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -5585,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="I139" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J139" t="s">
         <v>4</v>
@@ -5593,22 +5590,22 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B140" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C140" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
       <c r="E140" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F140" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -5619,22 +5616,22 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B141" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C141" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="E141" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F141" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -5645,22 +5642,22 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B142" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C142" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="E142" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F142" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -5677,7 +5674,7 @@
         <v>69</v>
       </c>
       <c r="C143" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D143" t="s">
         <v>13</v>
@@ -5695,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="I143" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J143" t="s">
         <v>4</v>
@@ -5703,13 +5700,13 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B144" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C144" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
@@ -5735,7 +5732,7 @@
         <v>80</v>
       </c>
       <c r="C145" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -5755,22 +5752,22 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C146" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F146" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -5781,22 +5778,22 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B147" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C147" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="E147" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F147" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -5807,22 +5804,22 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B148" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C148" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
       <c r="E148" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F148" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -5833,22 +5830,22 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B149" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C149" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F149" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -5859,22 +5856,22 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B150" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C150" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="E150" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F150" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -5885,22 +5882,22 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B151" t="s">
+        <v>291</v>
+      </c>
+      <c r="C151" t="s">
+        <v>107</v>
+      </c>
+      <c r="D151" t="s">
+        <v>5</v>
+      </c>
+      <c r="E151" t="s">
+        <v>110</v>
+      </c>
+      <c r="F151" t="s">
         <v>290</v>
-      </c>
-      <c r="C151" t="s">
-        <v>106</v>
-      </c>
-      <c r="D151" t="s">
-        <v>5</v>
-      </c>
-      <c r="E151" t="s">
-        <v>109</v>
-      </c>
-      <c r="F151" t="s">
-        <v>289</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -5911,22 +5908,22 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B152" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C152" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
       </c>
       <c r="E152" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F152" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -5937,22 +5934,22 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B153" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C153" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
       <c r="E153" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F153" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -5963,22 +5960,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B154" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C154" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
       <c r="E154" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F154" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -5989,22 +5986,22 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B155" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C155" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F155" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -6015,22 +6012,22 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B156" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C156" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="E156" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F156" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -6041,22 +6038,22 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B157" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C157" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
       <c r="E157" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F157" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -6067,22 +6064,22 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B158" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C158" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F158" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -6093,22 +6090,22 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B159" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="E159" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F159" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -6119,22 +6116,22 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B160" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C160" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
       <c r="E160" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F160" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -6148,10 +6145,10 @@
         <v>49</v>
       </c>
       <c r="B161" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C161" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -6169,7 +6166,7 @@
         <v>1</v>
       </c>
       <c r="I161" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J161" t="s">
         <v>24</v>
@@ -6177,22 +6174,22 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B162" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C162" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F162" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -6203,22 +6200,22 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B163" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C163" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F163" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -6229,22 +6226,22 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B164" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C164" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F164" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -6255,22 +6252,22 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B165" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C165" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F165" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -6284,19 +6281,19 @@
         <v>29</v>
       </c>
       <c r="B166" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C166" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="E166" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F166" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -6307,22 +6304,22 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B167" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C167" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="E167" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F167" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -6333,22 +6330,22 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B168" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C168" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="E168" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F168" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G168">
         <v>1</v>
@@ -6357,7 +6354,7 @@
         <v>1</v>
       </c>
       <c r="I168" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J168" t="s">
         <v>4</v>
@@ -6365,22 +6362,22 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B169" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C169" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F169" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -6391,22 +6388,22 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B170" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C170" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F170" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -6417,22 +6414,22 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B171" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C171" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="E171" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F171" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -6446,10 +6443,10 @@
         <v>7</v>
       </c>
       <c r="B172" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C172" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
@@ -6467,7 +6464,7 @@
         <v>2</v>
       </c>
       <c r="I172" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J172" t="s">
         <v>4</v>
@@ -6481,7 +6478,7 @@
         <v>400</v>
       </c>
       <c r="C173" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D173" t="s">
         <v>13</v>
@@ -6499,7 +6496,7 @@
         <v>2</v>
       </c>
       <c r="I173" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J173" t="s">
         <v>4</v>
@@ -6507,22 +6504,22 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B174" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C174" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F174" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -6533,22 +6530,22 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B175" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C175" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F175" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -6559,13 +6556,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B176" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C176" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -6588,10 +6585,10 @@
         <v>42</v>
       </c>
       <c r="B177" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C177" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -6609,7 +6606,7 @@
         <v>1</v>
       </c>
       <c r="I177" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J177" t="s">
         <v>26</v>
@@ -6623,7 +6620,7 @@
         <v>83</v>
       </c>
       <c r="C178" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
@@ -6641,10 +6638,10 @@
         <v>1</v>
       </c>
       <c r="I178" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J178" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.35">
@@ -6652,10 +6649,10 @@
         <v>73</v>
       </c>
       <c r="B179" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C179" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
@@ -6673,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="I179" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J179" t="s">
         <v>24</v>
@@ -6681,22 +6678,22 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B180" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C180" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
       <c r="E180" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F180" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G180">
         <v>1</v>
@@ -6707,22 +6704,22 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B181" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C181" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
       </c>
       <c r="E181" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F181" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -6733,22 +6730,22 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B182" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C182" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
       <c r="E182" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F182" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G182">
         <v>1</v>
@@ -6759,22 +6756,22 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B183" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C183" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
       <c r="E183" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F183" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G183">
         <v>1</v>
@@ -6785,22 +6782,22 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B184" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C184" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
       </c>
       <c r="E184" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F184" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -6811,22 +6808,22 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B185" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C185" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
       </c>
       <c r="E185" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F185" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -6837,22 +6834,22 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B186" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C186" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
       </c>
       <c r="E186" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F186" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -6863,22 +6860,22 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B187" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C187" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
       </c>
       <c r="E187" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F187" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -6889,22 +6886,22 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B188" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C188" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
       </c>
       <c r="E188" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F188" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -6915,22 +6912,22 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B189" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C189" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
       <c r="E189" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F189" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -6941,22 +6938,22 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B190" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C190" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
       </c>
       <c r="E190" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F190" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -6967,22 +6964,22 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B191" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C191" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
       </c>
       <c r="E191" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F191" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G191">
         <v>1</v>
@@ -6993,22 +6990,22 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B192" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C192" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
       </c>
       <c r="E192" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F192" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G192">
         <v>1</v>
@@ -7019,22 +7016,22 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B193" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C193" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D193" t="s">
         <v>5</v>
       </c>
       <c r="E193" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F193" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G193">
         <v>1</v>
@@ -7048,10 +7045,10 @@
         <v>23</v>
       </c>
       <c r="B194" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C194" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D194" t="s">
         <v>5</v>
@@ -7069,7 +7066,7 @@
         <v>1</v>
       </c>
       <c r="I194" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J194" t="s">
         <v>26</v>
@@ -7077,22 +7074,22 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B195" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C195" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D195" t="s">
         <v>5</v>
       </c>
       <c r="E195" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F195" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G195">
         <v>1</v>
@@ -7103,22 +7100,22 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B196" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C196" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D196" t="s">
         <v>5</v>
       </c>
       <c r="E196" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F196" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -7129,22 +7126,22 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B197" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C197" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D197" t="s">
         <v>5</v>
       </c>
       <c r="E197" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F197" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G197">
         <v>1</v>
@@ -7153,27 +7150,27 @@
         <v>1</v>
       </c>
       <c r="I197" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B198" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C198" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D198" t="s">
         <v>5</v>
       </c>
       <c r="E198" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F198" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -7184,19 +7181,19 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B199" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C199" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D199" t="s">
         <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F199" t="s">
         <v>12</v>
@@ -7210,22 +7207,22 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B200" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C200" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D200" t="s">
         <v>5</v>
       </c>
       <c r="E200" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F200" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G200">
         <v>1</v>
@@ -7236,22 +7233,22 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B201" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C201" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D201" t="s">
         <v>5</v>
       </c>
       <c r="E201" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F201" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G201">
         <v>1</v>
@@ -7260,7 +7257,7 @@
         <v>1</v>
       </c>
       <c r="I201" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J201" t="s">
         <v>26</v>
@@ -7268,22 +7265,22 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B202" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C202" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D202" t="s">
         <v>5</v>
       </c>
       <c r="E202" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F202" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G202">
         <v>1</v>
@@ -7294,22 +7291,22 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B203" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C203" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D203" t="s">
         <v>5</v>
       </c>
       <c r="E203" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F203" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G203">
         <v>1</v>
@@ -7320,22 +7317,22 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B204" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C204" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D204" t="s">
         <v>5</v>
       </c>
       <c r="E204" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F204" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -7346,22 +7343,22 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B205" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C205" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D205" t="s">
         <v>5</v>
       </c>
       <c r="E205" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F205" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G205">
         <v>1</v>
@@ -7372,13 +7369,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B206" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C206" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D206" t="s">
         <v>5</v>
@@ -7398,22 +7395,22 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B207" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C207" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D207" t="s">
         <v>5</v>
       </c>
       <c r="E207" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F207" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G207">
         <v>1</v>
@@ -7424,22 +7421,22 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B208" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C208" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D208" t="s">
         <v>5</v>
       </c>
       <c r="E208" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F208" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G208">
         <v>1</v>
@@ -7450,22 +7447,22 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B209" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C209" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D209" t="s">
         <v>5</v>
       </c>
       <c r="E209" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F209" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G209">
         <v>1</v>
@@ -7476,22 +7473,22 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B210" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C210" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D210" t="s">
         <v>5</v>
       </c>
       <c r="E210" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F210" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G210">
         <v>1</v>
@@ -7502,22 +7499,22 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B211" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C211" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D211" t="s">
         <v>5</v>
       </c>
       <c r="E211" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F211" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -7528,22 +7525,22 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B212" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C212" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D212" t="s">
         <v>5</v>
       </c>
       <c r="E212" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F212" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G212">
         <v>1</v>
@@ -7554,22 +7551,22 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B213" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C213" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D213" t="s">
         <v>5</v>
       </c>
       <c r="E213" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F213" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G213">
         <v>1</v>
@@ -7583,19 +7580,19 @@
         <v>43</v>
       </c>
       <c r="B214" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C214" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D214" t="s">
         <v>5</v>
       </c>
       <c r="E214" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F214" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G214">
         <v>1</v>
@@ -7604,7 +7601,7 @@
         <v>1</v>
       </c>
       <c r="I214" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J214" t="s">
         <v>4</v>
@@ -7618,7 +7615,7 @@
         <v>89</v>
       </c>
       <c r="C215" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D215" t="s">
         <v>5</v>
@@ -7644,7 +7641,7 @@
         <v>91</v>
       </c>
       <c r="C216" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D216" t="s">
         <v>5</v>
@@ -7662,7 +7659,7 @@
         <v>1</v>
       </c>
       <c r="I216" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J216" t="s">
         <v>26</v>

--- a/Clientes_25-26_frentes_padronizado.xlsx
+++ b/Clientes_25-26_frentes_padronizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas moreira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CD7219-AFF0-447B-AD66-67075051ED39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9D5D3A-A884-4FA1-A570-4373EC23F51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="400">
   <si>
     <t>Pedra</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>Diamante</t>
-  </si>
-  <si>
-    <t>Verde</t>
   </si>
   <si>
     <t>Vermelho</t>
@@ -1628,31 +1625,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>0</v>
@@ -1660,22 +1657,19 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" t="s">
         <v>110</v>
-      </c>
-      <c r="F2" t="s">
-        <v>111</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1684,7 +1678,7 @@
         <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J2" t="s">
         <v>4</v>
@@ -1692,22 +1686,19 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" t="s">
         <v>112</v>
-      </c>
-      <c r="C3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" t="s">
-        <v>113</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1716,7 +1707,7 @@
         <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
@@ -1724,22 +1715,19 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" t="s">
         <v>114</v>
-      </c>
-      <c r="C4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" t="s">
-        <v>115</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1748,7 +1736,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
@@ -1756,22 +1744,19 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1780,7 +1765,7 @@
         <v>8</v>
       </c>
       <c r="I5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
@@ -1788,22 +1773,19 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" t="s">
         <v>120</v>
       </c>
-      <c r="C6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>121</v>
-      </c>
-      <c r="F6" t="s">
-        <v>122</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1812,7 +1794,7 @@
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
@@ -1820,22 +1802,19 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" t="s">
         <v>117</v>
       </c>
-      <c r="C7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>118</v>
-      </c>
-      <c r="F7" t="s">
-        <v>119</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1844,7 +1823,7 @@
         <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
@@ -1852,22 +1831,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -1876,7 +1852,7 @@
         <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
@@ -1884,22 +1860,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>4</v>
@@ -1908,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
@@ -1916,22 +1889,19 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
       <c r="C10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1940,30 +1910,27 @@
         <v>4</v>
       </c>
       <c r="I10" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" t="s">
         <v>123</v>
-      </c>
-      <c r="J10" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -1972,30 +1939,27 @@
         <v>4</v>
       </c>
       <c r="I11" t="s">
+        <v>122</v>
+      </c>
+      <c r="J11" t="s">
         <v>123</v>
-      </c>
-      <c r="J11" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -2004,24 +1968,24 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" t="s">
         <v>123</v>
-      </c>
-      <c r="J12" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
         <v>2</v>
@@ -2036,39 +2000,36 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" t="s">
         <v>123</v>
-      </c>
-      <c r="J13" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>264</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
@@ -2076,22 +2037,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>265</v>
+        <v>392</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F15" t="s">
-        <v>231</v>
+        <v>118</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -2100,7 +2058,7 @@
         <v>3</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
@@ -2108,22 +2066,22 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>118</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -2132,7 +2090,7 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
@@ -2140,31 +2098,28 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>386</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="J17" t="s">
         <v>4</v>
@@ -2172,22 +2127,19 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18">
         <v>3</v>
@@ -2196,7 +2148,7 @@
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J18" t="s">
         <v>4</v>
@@ -2204,22 +2156,19 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
         <v>110</v>
-      </c>
-      <c r="F19" t="s">
-        <v>111</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -2228,7 +2177,7 @@
         <v>4</v>
       </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J19" t="s">
         <v>4</v>
@@ -2236,22 +2185,19 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" t="s">
         <v>129</v>
-      </c>
-      <c r="C20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" t="s">
-        <v>130</v>
       </c>
       <c r="G20">
         <v>3</v>
@@ -2260,7 +2206,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J20" t="s">
         <v>4</v>
@@ -2268,22 +2214,19 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" t="s">
         <v>133</v>
       </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>134</v>
-      </c>
-      <c r="F21" t="s">
-        <v>135</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -2294,22 +2237,19 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
         <v>131</v>
       </c>
-      <c r="B22" t="s">
-        <v>132</v>
-      </c>
       <c r="C22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
         <v>110</v>
-      </c>
-      <c r="F22" t="s">
-        <v>111</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -2320,22 +2260,19 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" t="s">
         <v>139</v>
-      </c>
-      <c r="C23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F23" t="s">
-        <v>140</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2346,22 +2283,19 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" t="s">
         <v>11</v>
-      </c>
-      <c r="B24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C24" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -2372,22 +2306,19 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" t="s">
         <v>137</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" t="s">
-        <v>134</v>
-      </c>
-      <c r="F25" t="s">
-        <v>138</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -2398,22 +2329,19 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
+        <v>133</v>
+      </c>
+      <c r="F26" t="s">
         <v>134</v>
-      </c>
-      <c r="F26" t="s">
-        <v>135</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -2424,54 +2352,48 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
         <v>142</v>
       </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F27" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-      <c r="H27">
-        <v>2</v>
-      </c>
-      <c r="I27" t="s">
-        <v>143</v>
-      </c>
       <c r="J27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -2480,30 +2402,27 @@
         <v>2</v>
       </c>
       <c r="I28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" t="s">
         <v>59</v>
       </c>
-      <c r="B29" t="s">
-        <v>60</v>
-      </c>
       <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
         <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>10</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -2512,27 +2431,24 @@
         <v>3</v>
       </c>
       <c r="I29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" t="s">
         <v>147</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" t="s">
-        <v>134</v>
-      </c>
-      <c r="F30" t="s">
-        <v>148</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -2541,27 +2457,24 @@
         <v>3</v>
       </c>
       <c r="I30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" t="s">
         <v>134</v>
-      </c>
-      <c r="F31" t="s">
-        <v>135</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2570,27 +2483,24 @@
         <v>3</v>
       </c>
       <c r="I31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E32" t="s">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -2599,28 +2509,25 @@
         <v>2</v>
       </c>
       <c r="J32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" t="s">
         <v>149</v>
       </c>
-      <c r="C33" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" t="s">
-        <v>110</v>
-      </c>
-      <c r="F33" t="s">
-        <v>150</v>
-      </c>
       <c r="G33">
         <v>2</v>
       </c>
@@ -2628,27 +2535,24 @@
         <v>2</v>
       </c>
       <c r="J33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" t="s">
         <v>134</v>
-      </c>
-      <c r="F34" t="s">
-        <v>135</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -2657,24 +2561,21 @@
         <v>4</v>
       </c>
       <c r="I34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E35" t="s">
         <v>2</v>
@@ -2689,30 +2590,27 @@
         <v>4</v>
       </c>
       <c r="I35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E36" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" t="s">
         <v>134</v>
-      </c>
-      <c r="F36" t="s">
-        <v>135</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2721,30 +2619,27 @@
         <v>4</v>
       </c>
       <c r="I36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E37" t="s">
+        <v>133</v>
+      </c>
+      <c r="F37" t="s">
         <v>134</v>
-      </c>
-      <c r="F37" t="s">
-        <v>135</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2753,24 +2648,21 @@
         <v>4</v>
       </c>
       <c r="I37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E38" t="s">
         <v>2</v>
@@ -2785,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="I38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J38" t="s">
         <v>4</v>
@@ -2793,22 +2685,19 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -2817,7 +2706,7 @@
         <v>2</v>
       </c>
       <c r="I39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J39" t="s">
         <v>4</v>
@@ -2825,22 +2714,19 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2849,27 +2735,24 @@
         <v>2</v>
       </c>
       <c r="I40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E41" t="s">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -2878,27 +2761,24 @@
         <v>2</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
         <v>53</v>
       </c>
-      <c r="B42" t="s">
-        <v>54</v>
-      </c>
       <c r="C42" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
         <v>2</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -2907,21 +2787,18 @@
         <v>6</v>
       </c>
       <c r="J42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
-      </c>
-      <c r="D43" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E43" t="s">
         <v>2</v>
@@ -2936,27 +2813,24 @@
         <v>6</v>
       </c>
       <c r="J43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C44" t="s">
-        <v>107</v>
-      </c>
-      <c r="D44" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s">
         <v>134</v>
-      </c>
-      <c r="F44" t="s">
-        <v>135</v>
       </c>
       <c r="G44">
         <v>2</v>
@@ -2965,27 +2839,24 @@
         <v>6</v>
       </c>
       <c r="J44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E45" t="s">
+        <v>133</v>
+      </c>
+      <c r="F45" t="s">
         <v>134</v>
-      </c>
-      <c r="F45" t="s">
-        <v>135</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -2994,27 +2865,24 @@
         <v>6</v>
       </c>
       <c r="J45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
-      </c>
-      <c r="D46" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E46" t="s">
+        <v>133</v>
+      </c>
+      <c r="F46" t="s">
         <v>134</v>
-      </c>
-      <c r="F46" t="s">
-        <v>135</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -3023,27 +2891,24 @@
         <v>6</v>
       </c>
       <c r="J46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
-      </c>
-      <c r="D47" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E47" t="s">
+        <v>133</v>
+      </c>
+      <c r="F47" t="s">
         <v>134</v>
-      </c>
-      <c r="F47" t="s">
-        <v>135</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -3052,28 +2917,25 @@
         <v>6</v>
       </c>
       <c r="J47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" t="s">
+        <v>163</v>
+      </c>
+      <c r="C48" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" t="s">
+        <v>109</v>
+      </c>
+      <c r="F48" t="s">
         <v>164</v>
       </c>
-      <c r="C48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
-      <c r="E48" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48" t="s">
-        <v>165</v>
-      </c>
       <c r="G48">
         <v>2</v>
       </c>
@@ -3081,24 +2943,21 @@
         <v>2</v>
       </c>
       <c r="I48" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E49" t="s">
         <v>2</v>
@@ -3113,30 +2972,27 @@
         <v>2</v>
       </c>
       <c r="I49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -3147,22 +3003,19 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" t="s">
         <v>166</v>
       </c>
-      <c r="B51" t="s">
-        <v>167</v>
-      </c>
       <c r="C51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E51" t="s">
         <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -3173,22 +3026,19 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>168</v>
+      </c>
+      <c r="B52" t="s">
         <v>169</v>
       </c>
-      <c r="B52" t="s">
-        <v>170</v>
-      </c>
       <c r="C52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E52" t="s">
         <v>2</v>
       </c>
       <c r="F52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G52">
         <v>2</v>
@@ -3199,22 +3049,19 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B53" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E53" t="s">
         <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -3225,22 +3072,19 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B54" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" t="s">
+        <v>106</v>
+      </c>
+      <c r="E54" t="s">
+        <v>133</v>
+      </c>
+      <c r="F54" t="s">
         <v>171</v>
-      </c>
-      <c r="C54" t="s">
-        <v>107</v>
-      </c>
-      <c r="D54" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" t="s">
-        <v>134</v>
-      </c>
-      <c r="F54" t="s">
-        <v>172</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -3251,22 +3095,19 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
-      </c>
-      <c r="D55" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E55" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -3275,7 +3116,7 @@
         <v>8</v>
       </c>
       <c r="I55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J55" t="s">
         <v>4</v>
@@ -3283,16 +3124,16 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E56" t="s">
         <v>2</v>
@@ -3307,7 +3148,7 @@
         <v>8</v>
       </c>
       <c r="I56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J56" t="s">
         <v>4</v>
@@ -3315,22 +3156,19 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
-      </c>
-      <c r="D57" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E57" t="s">
+        <v>133</v>
+      </c>
+      <c r="F57" t="s">
         <v>134</v>
-      </c>
-      <c r="F57" t="s">
-        <v>135</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -3339,7 +3177,7 @@
         <v>8</v>
       </c>
       <c r="I57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J57" t="s">
         <v>4</v>
@@ -3347,22 +3185,19 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C58" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E58" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -3371,7 +3206,7 @@
         <v>8</v>
       </c>
       <c r="I58" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J58" t="s">
         <v>4</v>
@@ -3379,22 +3214,19 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" t="s">
-        <v>107</v>
-      </c>
-      <c r="D59" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F59" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G59">
         <v>2</v>
@@ -3403,7 +3235,7 @@
         <v>8</v>
       </c>
       <c r="I59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J59" t="s">
         <v>4</v>
@@ -3411,22 +3243,19 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C60" t="s">
-        <v>107</v>
-      </c>
-      <c r="D60" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E60" t="s">
         <v>2</v>
       </c>
       <c r="F60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G60">
         <v>2</v>
@@ -3435,7 +3264,7 @@
         <v>8</v>
       </c>
       <c r="I60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J60" t="s">
         <v>4</v>
@@ -3443,22 +3272,19 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
-      </c>
-      <c r="D61" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -3467,7 +3293,7 @@
         <v>8</v>
       </c>
       <c r="I61" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J61" t="s">
         <v>4</v>
@@ -3475,22 +3301,22 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G62">
         <v>2</v>
@@ -3499,7 +3325,7 @@
         <v>8</v>
       </c>
       <c r="I62" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J62" t="s">
         <v>4</v>
@@ -3507,22 +3333,19 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
-      </c>
-      <c r="D63" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E63" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G63">
         <v>2</v>
@@ -3533,22 +3356,19 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B64" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>107</v>
-      </c>
-      <c r="D64" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G64">
         <v>2</v>
@@ -3559,22 +3379,19 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>178</v>
+      </c>
+      <c r="B65" t="s">
         <v>179</v>
       </c>
-      <c r="B65" t="s">
-        <v>180</v>
-      </c>
       <c r="C65" t="s">
-        <v>107</v>
-      </c>
-      <c r="D65" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G65">
         <v>2</v>
@@ -3585,22 +3402,19 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B66" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C66" t="s">
-        <v>107</v>
-      </c>
-      <c r="D66" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E66" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F66" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G66">
         <v>2</v>
@@ -3611,22 +3425,19 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
+        <v>389</v>
+      </c>
+      <c r="B67" t="s">
         <v>390</v>
       </c>
-      <c r="B67" t="s">
-        <v>391</v>
-      </c>
       <c r="C67" t="s">
-        <v>107</v>
-      </c>
-      <c r="D67" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E67" t="s">
         <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G67">
         <v>2</v>
@@ -3637,31 +3448,31 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
+        <v>106</v>
+      </c>
+      <c r="D68" t="s">
+        <v>5</v>
+      </c>
+      <c r="E68" t="s">
+        <v>2</v>
+      </c>
+      <c r="F68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68">
+        <v>2</v>
+      </c>
+      <c r="I68" t="s">
         <v>107</v>
-      </c>
-      <c r="D68" t="s">
-        <v>6</v>
-      </c>
-      <c r="E68" t="s">
-        <v>2</v>
-      </c>
-      <c r="F68" t="s">
-        <v>8</v>
-      </c>
-      <c r="G68">
-        <v>2</v>
-      </c>
-      <c r="H68">
-        <v>2</v>
-      </c>
-      <c r="I68" t="s">
-        <v>108</v>
       </c>
       <c r="J68" t="s">
         <v>4</v>
@@ -3669,31 +3480,28 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C69" t="s">
+        <v>106</v>
+      </c>
+      <c r="E69" t="s">
+        <v>133</v>
+      </c>
+      <c r="F69" t="s">
+        <v>134</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+      <c r="I69" t="s">
         <v>107</v>
-      </c>
-      <c r="D69" t="s">
-        <v>5</v>
-      </c>
-      <c r="E69" t="s">
-        <v>134</v>
-      </c>
-      <c r="F69" t="s">
-        <v>135</v>
-      </c>
-      <c r="G69">
-        <v>2</v>
-      </c>
-      <c r="H69">
-        <v>2</v>
-      </c>
-      <c r="I69" t="s">
-        <v>108</v>
       </c>
       <c r="J69" t="s">
         <v>4</v>
@@ -3701,112 +3509,91 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B70" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
-      </c>
-      <c r="D70" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E70" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F70" t="s">
-        <v>194</v>
+        <v>11</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
         <v>1</v>
+      </c>
+      <c r="I70" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
-      </c>
-      <c r="D71" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E71" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71">
-        <v>2</v>
-      </c>
-      <c r="I71" t="s">
-        <v>143</v>
-      </c>
-      <c r="J71" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="B72" t="s">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
-      </c>
-      <c r="D72" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E72" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>2</v>
-      </c>
-      <c r="I72" t="s">
-        <v>143</v>
-      </c>
-      <c r="J72" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>195</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="C73" t="s">
-        <v>107</v>
-      </c>
-      <c r="D73" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E73" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3817,22 +3604,19 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B74" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C74" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E74" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F74" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3843,54 +3627,42 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="B75" t="s">
-        <v>58</v>
+        <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D75" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E75" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="F75" t="s">
-        <v>28</v>
+        <v>193</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75">
-        <v>2</v>
-      </c>
-      <c r="I75" t="s">
-        <v>156</v>
-      </c>
-      <c r="J75" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="C76" t="s">
-        <v>107</v>
-      </c>
-      <c r="D76" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E76" t="s">
         <v>2</v>
       </c>
       <c r="F76" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3899,383 +3671,350 @@
         <v>2</v>
       </c>
       <c r="I76" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="J76" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B77" t="s">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
-      </c>
-      <c r="D77" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E77" t="s">
         <v>2</v>
       </c>
       <c r="F77" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="J77" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B78" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E78" t="s">
+        <v>133</v>
+      </c>
+      <c r="F78" t="s">
         <v>134</v>
       </c>
-      <c r="F78" t="s">
-        <v>135</v>
-      </c>
       <c r="G78">
         <v>1</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B79" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
-      </c>
-      <c r="D79" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E79" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F79" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>201</v>
+        <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>205</v>
+        <v>57</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
-      </c>
-      <c r="D80" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E80" t="s">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="F80" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
+        <v>2</v>
+      </c>
+      <c r="I80" t="s">
+        <v>155</v>
+      </c>
+      <c r="J80" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>201</v>
+        <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
-      </c>
-      <c r="D81" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E81" t="s">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="F81" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="G81">
         <v>1</v>
       </c>
       <c r="H81">
+        <v>2</v>
+      </c>
+      <c r="I81" t="s">
+        <v>155</v>
+      </c>
+      <c r="J81" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>201</v>
+        <v>16</v>
       </c>
       <c r="B82" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C82" t="s">
-        <v>107</v>
-      </c>
-      <c r="D82" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E82" t="s">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="F82" t="s">
-        <v>203</v>
+        <v>3</v>
       </c>
       <c r="G82">
         <v>1</v>
       </c>
       <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82" t="s">
+        <v>155</v>
+      </c>
+      <c r="J82" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B83" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C83" t="s">
-        <v>107</v>
-      </c>
-      <c r="D83" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E83" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G83">
         <v>1</v>
       </c>
       <c r="H83">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B84" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
-      </c>
-      <c r="D84" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E84" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G84">
         <v>1</v>
       </c>
       <c r="H84">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="C85" t="s">
-        <v>107</v>
-      </c>
-      <c r="D85" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E85" t="s">
-        <v>2</v>
+        <v>133</v>
       </c>
       <c r="F85" t="s">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="G85">
         <v>1</v>
       </c>
       <c r="H85">
-        <v>2</v>
-      </c>
-      <c r="I85" t="s">
-        <v>156</v>
-      </c>
-      <c r="J85" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B86" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C86" t="s">
-        <v>107</v>
-      </c>
-      <c r="D86" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E86" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F86" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G86">
         <v>1</v>
       </c>
       <c r="H86">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>1</v>
+        <v>206</v>
       </c>
       <c r="B87" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C87" t="s">
-        <v>107</v>
-      </c>
-      <c r="D87" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E87" t="s">
+        <v>133</v>
+      </c>
+      <c r="F87" t="s">
         <v>134</v>
       </c>
-      <c r="F87" t="s">
-        <v>199</v>
-      </c>
       <c r="G87">
         <v>1</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="B88" t="s">
-        <v>62</v>
+        <v>207</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
-      </c>
-      <c r="D88" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E88" t="s">
-        <v>2</v>
+        <v>133</v>
       </c>
       <c r="F88" t="s">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
       <c r="H88">
-        <v>1</v>
-      </c>
-      <c r="J88" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B89" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C89" t="s">
-        <v>107</v>
-      </c>
-      <c r="D89" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E89" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F89" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C90" t="s">
-        <v>107</v>
-      </c>
-      <c r="D90" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E90" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F90" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -4286,496 +4025,454 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>219</v>
+        <v>6</v>
       </c>
       <c r="B91" t="s">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="C91" t="s">
-        <v>107</v>
-      </c>
-      <c r="D91" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E91" t="s">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="F91" t="s">
-        <v>199</v>
+        <v>7</v>
       </c>
       <c r="G91">
         <v>1</v>
       </c>
       <c r="H91">
         <v>2</v>
+      </c>
+      <c r="I91" t="s">
+        <v>155</v>
+      </c>
+      <c r="J91" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>263</v>
+        <v>6</v>
       </c>
       <c r="B92" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="C92" t="s">
-        <v>107</v>
-      </c>
-      <c r="D92" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E92" t="s">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="F92" t="s">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="G92">
         <v>1</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I92" t="s">
+        <v>155</v>
+      </c>
+      <c r="J92" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>223</v>
+        <v>6</v>
       </c>
       <c r="B93" t="s">
-        <v>224</v>
+        <v>399</v>
       </c>
       <c r="C93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D93" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="G93">
         <v>1</v>
       </c>
       <c r="H93">
         <v>2</v>
+      </c>
+      <c r="I93" t="s">
+        <v>155</v>
+      </c>
+      <c r="J93" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B94" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C94" t="s">
-        <v>107</v>
-      </c>
-      <c r="D94" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E94" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F94" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="G94">
         <v>1</v>
       </c>
       <c r="H94">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>366</v>
+        <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>367</v>
+        <v>215</v>
       </c>
       <c r="C95" t="s">
-        <v>107</v>
-      </c>
-      <c r="D95" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E95" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F95" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="G95">
         <v>1</v>
       </c>
       <c r="H95">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
+        <v>216</v>
+      </c>
+      <c r="B96" t="s">
+        <v>217</v>
+      </c>
+      <c r="C96" t="s">
+        <v>106</v>
+      </c>
+      <c r="E96" t="s">
+        <v>109</v>
+      </c>
+      <c r="F96" t="s">
+        <v>193</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>218</v>
+      </c>
+      <c r="B97" t="s">
+        <v>220</v>
+      </c>
+      <c r="C97" t="s">
+        <v>106</v>
+      </c>
+      <c r="E97" t="s">
+        <v>133</v>
+      </c>
+      <c r="F97" t="s">
+        <v>221</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>218</v>
+      </c>
+      <c r="B98" t="s">
+        <v>219</v>
+      </c>
+      <c r="C98" t="s">
+        <v>106</v>
+      </c>
+      <c r="E98" t="s">
+        <v>133</v>
+      </c>
+      <c r="F98" t="s">
+        <v>198</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>222</v>
+      </c>
+      <c r="B99" t="s">
+        <v>223</v>
+      </c>
+      <c r="C99" t="s">
+        <v>106</v>
+      </c>
+      <c r="E99" t="s">
+        <v>109</v>
+      </c>
+      <c r="F99" t="s">
+        <v>164</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" t="s">
+        <v>106</v>
+      </c>
+      <c r="E100" t="s">
+        <v>109</v>
+      </c>
+      <c r="F100" t="s">
+        <v>164</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>225</v>
+      </c>
+      <c r="B101" t="s">
+        <v>226</v>
+      </c>
+      <c r="C101" t="s">
+        <v>106</v>
+      </c>
+      <c r="E101" t="s">
+        <v>133</v>
+      </c>
+      <c r="F101" t="s">
+        <v>202</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>225</v>
+      </c>
+      <c r="B102" t="s">
+        <v>227</v>
+      </c>
+      <c r="C102" t="s">
+        <v>106</v>
+      </c>
+      <c r="E102" t="s">
+        <v>133</v>
+      </c>
+      <c r="F102" t="s">
+        <v>134</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" t="s">
         <v>229</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C103" t="s">
+        <v>106</v>
+      </c>
+      <c r="E103" t="s">
+        <v>109</v>
+      </c>
+      <c r="F103" t="s">
         <v>230</v>
       </c>
-      <c r="C96" t="s">
-        <v>107</v>
-      </c>
-      <c r="D96" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" t="s">
-        <v>110</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>228</v>
+      </c>
+      <c r="B104" t="s">
         <v>231</v>
       </c>
-      <c r="G96">
-        <v>1</v>
-      </c>
-      <c r="H96">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>229</v>
-      </c>
-      <c r="B97" t="s">
+      <c r="C104" t="s">
+        <v>106</v>
+      </c>
+      <c r="E104" t="s">
+        <v>109</v>
+      </c>
+      <c r="F104" t="s">
+        <v>230</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>93</v>
+      </c>
+      <c r="B105" t="s">
+        <v>94</v>
+      </c>
+      <c r="C105" t="s">
+        <v>106</v>
+      </c>
+      <c r="E105" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" t="s">
+        <v>9</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
         <v>232</v>
       </c>
-      <c r="C97" t="s">
-        <v>107</v>
-      </c>
-      <c r="D97" t="s">
-        <v>5</v>
-      </c>
-      <c r="E97" t="s">
-        <v>110</v>
-      </c>
-      <c r="F97" t="s">
-        <v>231</v>
-      </c>
-      <c r="G97">
-        <v>1</v>
-      </c>
-      <c r="H97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>184</v>
-      </c>
-      <c r="B98" t="s">
-        <v>185</v>
-      </c>
-      <c r="C98" t="s">
-        <v>107</v>
-      </c>
-      <c r="D98" t="s">
-        <v>5</v>
-      </c>
-      <c r="E98" t="s">
-        <v>121</v>
-      </c>
-      <c r="F98" t="s">
-        <v>12</v>
-      </c>
-      <c r="G98">
-        <v>1</v>
-      </c>
-      <c r="H98">
-        <v>1</v>
-      </c>
-      <c r="I98" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>369</v>
-      </c>
-      <c r="B99" t="s">
-        <v>370</v>
-      </c>
-      <c r="C99" t="s">
-        <v>107</v>
-      </c>
-      <c r="D99" t="s">
-        <v>5</v>
-      </c>
-      <c r="E99" t="s">
-        <v>121</v>
-      </c>
-      <c r="F99" t="s">
-        <v>12</v>
-      </c>
-      <c r="G99">
-        <v>1</v>
-      </c>
-      <c r="H99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>33</v>
-      </c>
-      <c r="B100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C100" t="s">
-        <v>107</v>
-      </c>
-      <c r="D100" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" t="s">
-        <v>110</v>
-      </c>
-      <c r="F100" t="s">
-        <v>115</v>
-      </c>
-      <c r="G100">
-        <v>1</v>
-      </c>
-      <c r="H100">
-        <v>1</v>
-      </c>
-      <c r="I100" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>94</v>
-      </c>
-      <c r="B101" t="s">
-        <v>95</v>
-      </c>
-      <c r="C101" t="s">
-        <v>107</v>
-      </c>
-      <c r="D101" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101">
-        <v>1</v>
-      </c>
-      <c r="H101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+      <c r="B106" t="s">
         <v>233</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C106" t="s">
+        <v>106</v>
+      </c>
+      <c r="E106" t="s">
+        <v>133</v>
+      </c>
+      <c r="F106" t="s">
+        <v>198</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" t="s">
+        <v>235</v>
+      </c>
+      <c r="C107" t="s">
+        <v>106</v>
+      </c>
+      <c r="E107" t="s">
+        <v>133</v>
+      </c>
+      <c r="F107" t="s">
+        <v>198</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>232</v>
+      </c>
+      <c r="B108" t="s">
         <v>234</v>
       </c>
-      <c r="C102" t="s">
-        <v>107</v>
-      </c>
-      <c r="D102" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" t="s">
-        <v>134</v>
-      </c>
-      <c r="F102" t="s">
-        <v>199</v>
-      </c>
-      <c r="G102">
-        <v>1</v>
-      </c>
-      <c r="H102">
+      <c r="C108" t="s">
+        <v>106</v>
+      </c>
+      <c r="E108" t="s">
+        <v>133</v>
+      </c>
+      <c r="F108" t="s">
+        <v>198</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+      <c r="H108">
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>233</v>
-      </c>
-      <c r="B103" t="s">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
         <v>236</v>
       </c>
-      <c r="C103" t="s">
-        <v>107</v>
-      </c>
-      <c r="D103" t="s">
-        <v>5</v>
-      </c>
-      <c r="E103" t="s">
-        <v>134</v>
-      </c>
-      <c r="F103" t="s">
-        <v>199</v>
-      </c>
-      <c r="G103">
-        <v>1</v>
-      </c>
-      <c r="H103">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>233</v>
-      </c>
-      <c r="B104" t="s">
-        <v>235</v>
-      </c>
-      <c r="C104" t="s">
-        <v>107</v>
-      </c>
-      <c r="D104" t="s">
-        <v>5</v>
-      </c>
-      <c r="E104" t="s">
-        <v>134</v>
-      </c>
-      <c r="F104" t="s">
-        <v>199</v>
-      </c>
-      <c r="G104">
-        <v>1</v>
-      </c>
-      <c r="H104">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+      <c r="B109" t="s">
         <v>237</v>
       </c>
-      <c r="B105" t="s">
-        <v>238</v>
-      </c>
-      <c r="C105" t="s">
-        <v>107</v>
-      </c>
-      <c r="D105" t="s">
-        <v>5</v>
-      </c>
-      <c r="E105" t="s">
-        <v>134</v>
-      </c>
-      <c r="F105" t="s">
-        <v>172</v>
-      </c>
-      <c r="G105">
-        <v>1</v>
-      </c>
-      <c r="H105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>41</v>
-      </c>
-      <c r="B106" t="s">
-        <v>81</v>
-      </c>
-      <c r="C106" t="s">
-        <v>107</v>
-      </c>
-      <c r="D106" t="s">
-        <v>6</v>
-      </c>
-      <c r="E106" t="s">
-        <v>2</v>
-      </c>
-      <c r="F106" t="s">
-        <v>3</v>
-      </c>
-      <c r="G106">
-        <v>1</v>
-      </c>
-      <c r="H106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>41</v>
-      </c>
-      <c r="B107" t="s">
-        <v>75</v>
-      </c>
-      <c r="C107" t="s">
-        <v>107</v>
-      </c>
-      <c r="D107" t="s">
-        <v>5</v>
-      </c>
-      <c r="E107" t="s">
-        <v>2</v>
-      </c>
-      <c r="F107" t="s">
-        <v>8</v>
-      </c>
-      <c r="G107">
-        <v>1</v>
-      </c>
-      <c r="H107">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>186</v>
-      </c>
-      <c r="B108" t="s">
-        <v>187</v>
-      </c>
-      <c r="C108" t="s">
-        <v>107</v>
-      </c>
-      <c r="D108" t="s">
-        <v>5</v>
-      </c>
-      <c r="E108" t="s">
-        <v>110</v>
-      </c>
-      <c r="F108" t="s">
-        <v>165</v>
-      </c>
-      <c r="G108">
-        <v>1</v>
-      </c>
-      <c r="H108">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>239</v>
-      </c>
-      <c r="B109" t="s">
-        <v>240</v>
-      </c>
       <c r="C109" t="s">
-        <v>107</v>
-      </c>
-      <c r="D109" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E109" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F109" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -4784,15 +4481,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B110" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
@@ -4801,85 +4498,76 @@
         <v>2</v>
       </c>
       <c r="F110" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G110">
         <v>1</v>
       </c>
       <c r="H110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>241</v>
+        <v>40</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>74</v>
       </c>
       <c r="C111" t="s">
-        <v>107</v>
-      </c>
-      <c r="D111" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E111" t="s">
+        <v>2</v>
+      </c>
+      <c r="F111" t="s">
+        <v>7</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>238</v>
+      </c>
+      <c r="B112" t="s">
+        <v>239</v>
+      </c>
+      <c r="C112" t="s">
+        <v>106</v>
+      </c>
+      <c r="E112" t="s">
+        <v>133</v>
+      </c>
+      <c r="F112" t="s">
         <v>134</v>
       </c>
-      <c r="F111" t="s">
-        <v>199</v>
-      </c>
-      <c r="G111">
-        <v>1</v>
-      </c>
-      <c r="H111">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>241</v>
-      </c>
-      <c r="B112" t="s">
-        <v>242</v>
-      </c>
-      <c r="C112" t="s">
-        <v>107</v>
-      </c>
-      <c r="D112" t="s">
-        <v>5</v>
-      </c>
-      <c r="E112" t="s">
-        <v>134</v>
-      </c>
-      <c r="F112" t="s">
-        <v>135</v>
-      </c>
       <c r="G112">
         <v>1</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>244</v>
+        <v>54</v>
       </c>
       <c r="B113" t="s">
-        <v>245</v>
+        <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>107</v>
-      </c>
-      <c r="D113" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E113" t="s">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>194</v>
+        <v>7</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -4890,100 +4578,88 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B114" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C114" t="s">
-        <v>107</v>
-      </c>
-      <c r="D114" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E114" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F114" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G114">
         <v>1</v>
       </c>
       <c r="H114">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B115" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
-      </c>
-      <c r="D115" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E115" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F115" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="G115">
         <v>1</v>
       </c>
       <c r="H115">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>395</v>
+        <v>244</v>
       </c>
       <c r="C116" t="s">
-        <v>107</v>
-      </c>
-      <c r="D116" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E116" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F116" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G116">
         <v>1</v>
       </c>
       <c r="H116">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
+        <v>245</v>
+      </c>
+      <c r="B117" t="s">
         <v>246</v>
       </c>
-      <c r="B117" t="s">
-        <v>397</v>
-      </c>
       <c r="C117" t="s">
-        <v>107</v>
-      </c>
-      <c r="D117" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E117" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F117" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -4994,22 +4670,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B118" t="s">
-        <v>396</v>
+        <v>247</v>
       </c>
       <c r="C118" t="s">
-        <v>107</v>
-      </c>
-      <c r="D118" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E118" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F118" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -5020,22 +4693,19 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B119" t="s">
-        <v>249</v>
+        <v>394</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
-      </c>
-      <c r="D119" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E119" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F119" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -5046,22 +4716,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B120" t="s">
-        <v>250</v>
+        <v>396</v>
       </c>
       <c r="C120" t="s">
-        <v>107</v>
-      </c>
-      <c r="D120" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E120" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F120" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -5072,22 +4739,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B121" t="s">
-        <v>251</v>
+        <v>395</v>
       </c>
       <c r="C121" t="s">
-        <v>107</v>
-      </c>
-      <c r="D121" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F121" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -5098,22 +4762,19 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B122" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C122" t="s">
-        <v>107</v>
-      </c>
-      <c r="D122" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F122" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -5124,22 +4785,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B123" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C123" t="s">
-        <v>107</v>
-      </c>
-      <c r="D123" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E123" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F123" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -5150,22 +4808,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B124" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C124" t="s">
-        <v>107</v>
-      </c>
-      <c r="D124" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E124" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F124" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -5176,22 +4831,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B125" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C125" t="s">
-        <v>107</v>
-      </c>
-      <c r="D125" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E125" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F125" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -5202,100 +4854,88 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="B126" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="C126" t="s">
-        <v>107</v>
-      </c>
-      <c r="D126" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E126" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F126" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="G126">
         <v>1</v>
       </c>
       <c r="H126">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="B127" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C127" t="s">
-        <v>107</v>
-      </c>
-      <c r="D127" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E127" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F127" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="G127">
         <v>1</v>
       </c>
       <c r="H127">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B128" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C128" t="s">
-        <v>107</v>
-      </c>
-      <c r="D128" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E128" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F128" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="G128">
         <v>1</v>
       </c>
       <c r="H128">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>384</v>
+        <v>255</v>
       </c>
       <c r="B129" t="s">
-        <v>385</v>
+        <v>256</v>
       </c>
       <c r="C129" t="s">
-        <v>107</v>
-      </c>
-      <c r="D129" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E129" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F129" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -5306,22 +4946,19 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B130" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C130" t="s">
-        <v>107</v>
-      </c>
-      <c r="D130" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E130" t="s">
         <v>2</v>
       </c>
       <c r="F130" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -5330,39 +4967,36 @@
         <v>1</v>
       </c>
       <c r="I130" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J130" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C131" t="s">
+        <v>106</v>
+      </c>
+      <c r="E131" t="s">
+        <v>109</v>
+      </c>
+      <c r="F131" t="s">
+        <v>164</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131" t="s">
         <v>107</v>
-      </c>
-      <c r="D131" t="s">
-        <v>5</v>
-      </c>
-      <c r="E131" t="s">
-        <v>110</v>
-      </c>
-      <c r="F131" t="s">
-        <v>165</v>
-      </c>
-      <c r="G131">
-        <v>1</v>
-      </c>
-      <c r="H131">
-        <v>1</v>
-      </c>
-      <c r="I131" t="s">
-        <v>108</v>
       </c>
       <c r="J131" t="s">
         <v>4</v>
@@ -5370,22 +5004,19 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
+        <v>258</v>
+      </c>
+      <c r="B132" t="s">
         <v>259</v>
       </c>
-      <c r="B132" t="s">
-        <v>260</v>
-      </c>
       <c r="C132" t="s">
-        <v>107</v>
-      </c>
-      <c r="D132" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E132" t="s">
+        <v>8</v>
+      </c>
+      <c r="F132" t="s">
         <v>9</v>
-      </c>
-      <c r="F132" t="s">
-        <v>10</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -5396,22 +5027,19 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
+        <v>260</v>
+      </c>
+      <c r="B133" t="s">
         <v>261</v>
       </c>
-      <c r="B133" t="s">
-        <v>262</v>
-      </c>
       <c r="C133" t="s">
-        <v>107</v>
-      </c>
-      <c r="D133" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E133" t="s">
+        <v>133</v>
+      </c>
+      <c r="F133" t="s">
         <v>134</v>
-      </c>
-      <c r="F133" t="s">
-        <v>135</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -5422,48 +5050,42 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="B134" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="C134" t="s">
-        <v>107</v>
-      </c>
-      <c r="D134" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E134" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F134" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G134">
         <v>1</v>
       </c>
       <c r="H134">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B135" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C135" t="s">
-        <v>107</v>
-      </c>
-      <c r="D135" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E135" t="s">
         <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -5474,22 +5096,19 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
+        <v>265</v>
+      </c>
+      <c r="B136" t="s">
         <v>266</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
+        <v>106</v>
+      </c>
+      <c r="E136" t="s">
+        <v>133</v>
+      </c>
+      <c r="F136" t="s">
         <v>267</v>
-      </c>
-      <c r="C136" t="s">
-        <v>107</v>
-      </c>
-      <c r="D136" t="s">
-        <v>5</v>
-      </c>
-      <c r="E136" t="s">
-        <v>134</v>
-      </c>
-      <c r="F136" t="s">
-        <v>268</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -5500,22 +5119,19 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B137" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C137" t="s">
-        <v>107</v>
-      </c>
-      <c r="D137" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E137" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F137" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -5526,54 +5142,42 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B138" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C138" t="s">
-        <v>107</v>
-      </c>
-      <c r="D138" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E138" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F138" t="s">
-        <v>111</v>
+        <v>271</v>
       </c>
       <c r="G138">
         <v>1</v>
       </c>
       <c r="H138">
         <v>1</v>
-      </c>
-      <c r="I138" t="s">
-        <v>123</v>
-      </c>
-      <c r="J138" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>31</v>
+        <v>272</v>
       </c>
       <c r="B139" t="s">
-        <v>70</v>
+        <v>273</v>
       </c>
       <c r="C139" t="s">
-        <v>107</v>
-      </c>
-      <c r="D139" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E139" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="F139" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -5582,56 +5186,56 @@
         <v>1</v>
       </c>
       <c r="I139" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="J139" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>275</v>
+        <v>30</v>
       </c>
       <c r="B140" t="s">
-        <v>276</v>
+        <v>69</v>
       </c>
       <c r="C140" t="s">
-        <v>107</v>
-      </c>
-      <c r="D140" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E140" t="s">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="F140" t="s">
-        <v>194</v>
+        <v>31</v>
       </c>
       <c r="G140">
         <v>1</v>
       </c>
       <c r="H140">
         <v>1</v>
+      </c>
+      <c r="I140" t="s">
+        <v>142</v>
+      </c>
+      <c r="J140" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B141" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C141" t="s">
-        <v>107</v>
-      </c>
-      <c r="D141" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E141" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F141" t="s">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -5642,22 +5246,19 @@
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B142" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C142" t="s">
-        <v>107</v>
-      </c>
-      <c r="D142" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E142" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F142" t="s">
-        <v>165</v>
+        <v>278</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -5668,80 +5269,74 @@
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>38</v>
+        <v>279</v>
       </c>
       <c r="B143" t="s">
-        <v>69</v>
+        <v>280</v>
       </c>
       <c r="C143" t="s">
-        <v>107</v>
-      </c>
-      <c r="D143" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E143" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="F143" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="G143">
         <v>1</v>
       </c>
       <c r="H143">
         <v>1</v>
-      </c>
-      <c r="I143" t="s">
-        <v>127</v>
-      </c>
-      <c r="J143" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="B144" t="s">
-        <v>389</v>
+        <v>68</v>
       </c>
       <c r="C144" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D144" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E144" t="s">
         <v>2</v>
       </c>
       <c r="F144" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G144">
         <v>1</v>
       </c>
       <c r="H144">
         <v>1</v>
+      </c>
+      <c r="I144" t="s">
+        <v>126</v>
+      </c>
+      <c r="J144" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>79</v>
+        <v>387</v>
       </c>
       <c r="B145" t="s">
-        <v>80</v>
+        <v>388</v>
       </c>
       <c r="C145" t="s">
-        <v>107</v>
-      </c>
-      <c r="D145" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E145" t="s">
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -5752,22 +5347,19 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="B146" t="s">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="C146" t="s">
-        <v>107</v>
-      </c>
-      <c r="D146" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E146" t="s">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -5778,22 +5370,19 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B147" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C147" t="s">
-        <v>107</v>
-      </c>
-      <c r="D147" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E147" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F147" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -5804,22 +5393,19 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B148" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C148" t="s">
-        <v>107</v>
-      </c>
-      <c r="D148" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E148" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F148" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -5830,22 +5416,19 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B149" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C149" t="s">
-        <v>107</v>
-      </c>
-      <c r="D149" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E149" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F149" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -5856,22 +5439,19 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
+        <v>287</v>
+      </c>
+      <c r="B150" t="s">
         <v>288</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
+        <v>106</v>
+      </c>
+      <c r="E150" t="s">
+        <v>109</v>
+      </c>
+      <c r="F150" t="s">
         <v>289</v>
-      </c>
-      <c r="C150" t="s">
-        <v>107</v>
-      </c>
-      <c r="D150" t="s">
-        <v>5</v>
-      </c>
-      <c r="E150" t="s">
-        <v>110</v>
-      </c>
-      <c r="F150" t="s">
-        <v>290</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -5882,22 +5462,19 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B151" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C151" t="s">
-        <v>107</v>
-      </c>
-      <c r="D151" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E151" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F151" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -5908,22 +5485,19 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
+        <v>291</v>
+      </c>
+      <c r="B152" t="s">
         <v>292</v>
       </c>
-      <c r="B152" t="s">
-        <v>293</v>
-      </c>
       <c r="C152" t="s">
-        <v>107</v>
-      </c>
-      <c r="D152" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E152" t="s">
+        <v>133</v>
+      </c>
+      <c r="F152" t="s">
         <v>134</v>
-      </c>
-      <c r="F152" t="s">
-        <v>135</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -5934,22 +5508,19 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B153" t="s">
+        <v>293</v>
+      </c>
+      <c r="C153" t="s">
+        <v>106</v>
+      </c>
+      <c r="E153" t="s">
+        <v>133</v>
+      </c>
+      <c r="F153" t="s">
         <v>294</v>
-      </c>
-      <c r="C153" t="s">
-        <v>107</v>
-      </c>
-      <c r="D153" t="s">
-        <v>5</v>
-      </c>
-      <c r="E153" t="s">
-        <v>134</v>
-      </c>
-      <c r="F153" t="s">
-        <v>295</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -5960,22 +5531,19 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
+        <v>295</v>
+      </c>
+      <c r="B154" t="s">
         <v>296</v>
       </c>
-      <c r="B154" t="s">
-        <v>297</v>
-      </c>
       <c r="C154" t="s">
-        <v>107</v>
-      </c>
-      <c r="D154" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E154" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F154" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -5986,22 +5554,19 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B155" t="s">
+        <v>297</v>
+      </c>
+      <c r="C155" t="s">
+        <v>106</v>
+      </c>
+      <c r="E155" t="s">
+        <v>109</v>
+      </c>
+      <c r="F155" t="s">
         <v>298</v>
-      </c>
-      <c r="C155" t="s">
-        <v>107</v>
-      </c>
-      <c r="D155" t="s">
-        <v>5</v>
-      </c>
-      <c r="E155" t="s">
-        <v>110</v>
-      </c>
-      <c r="F155" t="s">
-        <v>299</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -6012,22 +5577,19 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B156" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C156" t="s">
-        <v>107</v>
-      </c>
-      <c r="D156" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E156" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F156" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -6038,22 +5600,19 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B157" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C157" t="s">
-        <v>107</v>
-      </c>
-      <c r="D157" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E157" t="s">
+        <v>133</v>
+      </c>
+      <c r="F157" t="s">
         <v>134</v>
-      </c>
-      <c r="F157" t="s">
-        <v>135</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -6064,22 +5623,19 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
+        <v>299</v>
+      </c>
+      <c r="B158" t="s">
         <v>300</v>
       </c>
-      <c r="B158" t="s">
-        <v>301</v>
-      </c>
       <c r="C158" t="s">
-        <v>107</v>
-      </c>
-      <c r="D158" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E158" t="s">
+        <v>133</v>
+      </c>
+      <c r="F158" t="s">
         <v>134</v>
-      </c>
-      <c r="F158" t="s">
-        <v>135</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -6090,22 +5646,19 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B159" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C159" t="s">
-        <v>107</v>
-      </c>
-      <c r="D159" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E159" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F159" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -6116,22 +5669,19 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B160" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C160" t="s">
-        <v>107</v>
-      </c>
-      <c r="D160" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E160" t="s">
+        <v>133</v>
+      </c>
+      <c r="F160" t="s">
         <v>134</v>
-      </c>
-      <c r="F160" t="s">
-        <v>135</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -6142,22 +5692,19 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B161" t="s">
-        <v>306</v>
+        <v>61</v>
       </c>
       <c r="C161" t="s">
-        <v>107</v>
-      </c>
-      <c r="D161" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E161" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F161" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -6165,83 +5712,80 @@
       <c r="H161">
         <v>1</v>
       </c>
-      <c r="I161" t="s">
-        <v>143</v>
-      </c>
       <c r="J161" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>307</v>
+        <v>32</v>
       </c>
       <c r="B162" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C162" t="s">
-        <v>107</v>
-      </c>
-      <c r="D162" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E162" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F162" t="s">
-        <v>199</v>
+        <v>114</v>
       </c>
       <c r="G162">
         <v>1</v>
       </c>
       <c r="H162">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="I162" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>307</v>
+        <v>48</v>
       </c>
       <c r="B163" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C163" t="s">
-        <v>107</v>
-      </c>
-      <c r="D163" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E163" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F163" t="s">
-        <v>172</v>
+        <v>49</v>
       </c>
       <c r="G163">
         <v>1</v>
       </c>
       <c r="H163">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="I163" t="s">
+        <v>142</v>
+      </c>
+      <c r="J163" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B164" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C164" t="s">
-        <v>107</v>
-      </c>
-      <c r="D164" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E164" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F164" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -6252,22 +5796,19 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B165" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C165" t="s">
-        <v>107</v>
-      </c>
-      <c r="D165" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E165" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F165" t="s">
-        <v>295</v>
+        <v>171</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -6278,106 +5819,88 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>29</v>
+        <v>306</v>
       </c>
       <c r="B166" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C166" t="s">
-        <v>107</v>
-      </c>
-      <c r="D166" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E166" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F166" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="G166">
         <v>1</v>
       </c>
       <c r="H166">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="B167" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="C167" t="s">
-        <v>107</v>
-      </c>
-      <c r="D167" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E167" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F167" t="s">
-        <v>231</v>
+        <v>294</v>
       </c>
       <c r="G167">
         <v>1</v>
       </c>
       <c r="H167">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>315</v>
+        <v>28</v>
       </c>
       <c r="B168" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C168" t="s">
-        <v>107</v>
-      </c>
-      <c r="D168" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E168" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F168" t="s">
-        <v>317</v>
+        <v>193</v>
       </c>
       <c r="G168">
         <v>1</v>
       </c>
       <c r="H168">
         <v>1</v>
-      </c>
-      <c r="I168" t="s">
-        <v>151</v>
-      </c>
-      <c r="J168" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B169" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C169" t="s">
-        <v>107</v>
-      </c>
-      <c r="D169" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E169" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F169" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -6388,138 +5911,117 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B170" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C170" t="s">
-        <v>107</v>
-      </c>
-      <c r="D170" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E170" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F170" t="s">
-        <v>165</v>
+        <v>316</v>
       </c>
       <c r="G170">
         <v>1</v>
       </c>
       <c r="H170">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I170" t="s">
+        <v>150</v>
+      </c>
+      <c r="J170" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B171" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C171" t="s">
-        <v>107</v>
-      </c>
-      <c r="D171" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E171" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F171" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="G171">
         <v>1</v>
       </c>
       <c r="H171">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>7</v>
+        <v>319</v>
       </c>
       <c r="B172" t="s">
-        <v>213</v>
+        <v>320</v>
       </c>
       <c r="C172" t="s">
-        <v>107</v>
-      </c>
-      <c r="D172" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E172" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="F172" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="G172">
         <v>1</v>
       </c>
       <c r="H172">
         <v>2</v>
-      </c>
-      <c r="I172" t="s">
-        <v>156</v>
-      </c>
-      <c r="J172" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>7</v>
+        <v>319</v>
       </c>
       <c r="B173" t="s">
-        <v>400</v>
+        <v>321</v>
       </c>
       <c r="C173" t="s">
-        <v>107</v>
-      </c>
-      <c r="D173" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E173" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="F173" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="G173">
         <v>1</v>
       </c>
       <c r="H173">
         <v>2</v>
-      </c>
-      <c r="I173" t="s">
-        <v>156</v>
-      </c>
-      <c r="J173" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
+        <v>322</v>
+      </c>
+      <c r="B174" t="s">
         <v>323</v>
       </c>
-      <c r="B174" t="s">
-        <v>324</v>
-      </c>
       <c r="C174" t="s">
-        <v>107</v>
-      </c>
-      <c r="D174" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E174" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F174" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -6530,22 +6032,19 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
+        <v>324</v>
+      </c>
+      <c r="B175" t="s">
         <v>325</v>
       </c>
-      <c r="B175" t="s">
-        <v>326</v>
-      </c>
       <c r="C175" t="s">
-        <v>107</v>
-      </c>
-      <c r="D175" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E175" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F175" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -6556,22 +6055,19 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
+        <v>326</v>
+      </c>
+      <c r="B176" t="s">
         <v>327</v>
       </c>
-      <c r="B176" t="s">
-        <v>328</v>
-      </c>
       <c r="C176" t="s">
-        <v>107</v>
-      </c>
-      <c r="D176" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E176" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F176" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G176">
         <v>1</v>
@@ -6582,54 +6078,42 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>42</v>
+        <v>328</v>
       </c>
       <c r="B177" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C177" t="s">
-        <v>107</v>
-      </c>
-      <c r="D177" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E177" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="F177" t="s">
-        <v>10</v>
+        <v>230</v>
       </c>
       <c r="G177">
         <v>1</v>
       </c>
       <c r="H177">
         <v>1</v>
-      </c>
-      <c r="I177" t="s">
-        <v>123</v>
-      </c>
-      <c r="J177" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="B178" t="s">
-        <v>83</v>
+        <v>330</v>
       </c>
       <c r="C178" t="s">
-        <v>107</v>
-      </c>
-      <c r="D178" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E178" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F178" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G178">
         <v>1</v>
@@ -6638,30 +6122,27 @@
         <v>1</v>
       </c>
       <c r="I178" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="J178" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B179" t="s">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="C179" t="s">
-        <v>107</v>
-      </c>
-      <c r="D179" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E179" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G179">
         <v>1</v>
@@ -6670,56 +6151,56 @@
         <v>1</v>
       </c>
       <c r="I179" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="J179" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>333</v>
+        <v>72</v>
       </c>
       <c r="B180" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C180" t="s">
-        <v>107</v>
-      </c>
-      <c r="D180" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E180" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="F180" t="s">
-        <v>194</v>
+        <v>9</v>
       </c>
       <c r="G180">
         <v>1</v>
       </c>
       <c r="H180">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="I180" t="s">
+        <v>142</v>
+      </c>
+      <c r="J180" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
+        <v>332</v>
+      </c>
+      <c r="B181" t="s">
         <v>333</v>
       </c>
-      <c r="B181" t="s">
-        <v>335</v>
-      </c>
       <c r="C181" t="s">
-        <v>107</v>
-      </c>
-      <c r="D181" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E181" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F181" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -6730,22 +6211,19 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B182" t="s">
-        <v>398</v>
+        <v>334</v>
       </c>
       <c r="C182" t="s">
-        <v>107</v>
-      </c>
-      <c r="D182" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E182" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F182" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G182">
         <v>1</v>
@@ -6756,22 +6234,19 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B183" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C183" t="s">
-        <v>107</v>
-      </c>
-      <c r="D183" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E183" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F183" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G183">
         <v>1</v>
@@ -6782,22 +6257,19 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B184" t="s">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="C184" t="s">
-        <v>107</v>
-      </c>
-      <c r="D184" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E184" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F184" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -6808,22 +6280,19 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B185" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C185" t="s">
-        <v>107</v>
-      </c>
-      <c r="D185" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E185" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F185" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -6834,22 +6303,19 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B186" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C186" t="s">
-        <v>107</v>
-      </c>
-      <c r="D186" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E186" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F186" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -6860,22 +6326,19 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B187" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C187" t="s">
-        <v>107</v>
-      </c>
-      <c r="D187" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E187" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F187" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -6886,22 +6349,19 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B188" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C188" t="s">
-        <v>107</v>
-      </c>
-      <c r="D188" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E188" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F188" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -6912,22 +6372,19 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B189" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C189" t="s">
-        <v>107</v>
-      </c>
-      <c r="D189" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E189" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F189" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -6938,22 +6395,19 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B190" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C190" t="s">
-        <v>107</v>
-      </c>
-      <c r="D190" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E190" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F190" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -6964,132 +6418,111 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="B191" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C191" t="s">
-        <v>107</v>
-      </c>
-      <c r="D191" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E191" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F191" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="G191">
         <v>1</v>
       </c>
       <c r="H191">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="B192" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C192" t="s">
-        <v>107</v>
-      </c>
-      <c r="D192" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E192" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F192" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G192">
         <v>1</v>
       </c>
       <c r="H192">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B193" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C193" t="s">
-        <v>107</v>
-      </c>
-      <c r="D193" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E193" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F193" t="s">
-        <v>194</v>
+        <v>114</v>
       </c>
       <c r="G193">
         <v>1</v>
       </c>
       <c r="H193">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>23</v>
+        <v>345</v>
       </c>
       <c r="B194" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C194" t="s">
-        <v>107</v>
-      </c>
-      <c r="D194" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E194" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="F194" t="s">
-        <v>3</v>
+        <v>164</v>
       </c>
       <c r="G194">
         <v>1</v>
       </c>
       <c r="H194">
         <v>1</v>
-      </c>
-      <c r="I194" t="s">
-        <v>143</v>
-      </c>
-      <c r="J194" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B195" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C195" t="s">
-        <v>107</v>
-      </c>
-      <c r="D195" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E195" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F195" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="G195">
         <v>1</v>
@@ -7100,22 +6533,19 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B196" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C196" t="s">
-        <v>107</v>
-      </c>
-      <c r="D196" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E196" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F196" t="s">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -7126,22 +6556,19 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>355</v>
+        <v>22</v>
       </c>
       <c r="B197" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C197" t="s">
-        <v>107</v>
-      </c>
-      <c r="D197" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E197" t="s">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="F197" t="s">
-        <v>165</v>
+        <v>3</v>
       </c>
       <c r="G197">
         <v>1</v>
@@ -7150,163 +6577,145 @@
         <v>1</v>
       </c>
       <c r="I197" t="s">
-        <v>357</v>
+        <v>142</v>
+      </c>
+      <c r="J197" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B198" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C198" t="s">
-        <v>107</v>
-      </c>
-      <c r="D198" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E198" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F198" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="G198">
         <v>1</v>
       </c>
       <c r="H198">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B199" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C199" t="s">
-        <v>107</v>
-      </c>
-      <c r="D199" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E199" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F199" t="s">
-        <v>12</v>
+        <v>230</v>
       </c>
       <c r="G199">
         <v>1</v>
       </c>
       <c r="H199">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B200" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C200" t="s">
-        <v>107</v>
-      </c>
-      <c r="D200" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E200" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F200" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="G200">
         <v>1</v>
       </c>
       <c r="H200">
         <v>1</v>
+      </c>
+      <c r="I200" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B201" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C201" t="s">
-        <v>107</v>
-      </c>
-      <c r="D201" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E201" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F201" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G201">
         <v>1</v>
       </c>
       <c r="H201">
         <v>1</v>
-      </c>
-      <c r="I201" t="s">
-        <v>151</v>
-      </c>
-      <c r="J201" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B202" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C202" t="s">
-        <v>107</v>
-      </c>
-      <c r="D202" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E202" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F202" t="s">
-        <v>231</v>
+        <v>11</v>
       </c>
       <c r="G202">
         <v>1</v>
       </c>
       <c r="H202">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>190</v>
+        <v>361</v>
       </c>
       <c r="B203" t="s">
-        <v>191</v>
+        <v>362</v>
       </c>
       <c r="C203" t="s">
-        <v>107</v>
-      </c>
-      <c r="D203" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E203" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F203" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="G203">
         <v>1</v>
@@ -7317,48 +6726,48 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="B204" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="C204" t="s">
-        <v>107</v>
-      </c>
-      <c r="D204" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E204" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F204" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="G204">
         <v>1</v>
       </c>
       <c r="H204">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="I204" t="s">
+        <v>150</v>
+      </c>
+      <c r="J204" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B205" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="C205" t="s">
-        <v>107</v>
-      </c>
-      <c r="D205" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E205" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F205" t="s">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="G205">
         <v>1</v>
@@ -7369,48 +6778,42 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>188</v>
+        <v>365</v>
       </c>
       <c r="B206" t="s">
-        <v>189</v>
+        <v>367</v>
       </c>
       <c r="C206" t="s">
-        <v>107</v>
-      </c>
-      <c r="D206" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E206" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="F206" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G206">
         <v>1</v>
       </c>
       <c r="H206">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B207" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C207" t="s">
-        <v>107</v>
-      </c>
-      <c r="D207" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E207" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F207" t="s">
-        <v>165</v>
+        <v>11</v>
       </c>
       <c r="G207">
         <v>1</v>
@@ -7421,48 +6824,42 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B208" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C208" t="s">
-        <v>107</v>
-      </c>
-      <c r="D208" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E208" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F208" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="G208">
         <v>1</v>
       </c>
       <c r="H208">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B209" t="s">
         <v>374</v>
       </c>
       <c r="C209" t="s">
-        <v>107</v>
-      </c>
-      <c r="D209" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E209" t="s">
+        <v>133</v>
+      </c>
+      <c r="F209" t="s">
         <v>134</v>
-      </c>
-      <c r="F209" t="s">
-        <v>135</v>
       </c>
       <c r="G209">
         <v>1</v>
@@ -7473,48 +6870,42 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>270</v>
+        <v>372</v>
       </c>
       <c r="B210" t="s">
-        <v>271</v>
+        <v>373</v>
       </c>
       <c r="C210" t="s">
-        <v>107</v>
-      </c>
-      <c r="D210" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E210" t="s">
+        <v>133</v>
+      </c>
+      <c r="F210" t="s">
         <v>134</v>
       </c>
-      <c r="F210" t="s">
-        <v>272</v>
-      </c>
       <c r="G210">
         <v>1</v>
       </c>
       <c r="H210">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
+        <v>375</v>
+      </c>
+      <c r="B211" t="s">
         <v>376</v>
       </c>
-      <c r="B211" t="s">
-        <v>377</v>
-      </c>
       <c r="C211" t="s">
-        <v>107</v>
-      </c>
-      <c r="D211" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E211" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F211" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -7525,22 +6916,19 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
+        <v>377</v>
+      </c>
+      <c r="B212" t="s">
         <v>378</v>
       </c>
-      <c r="B212" t="s">
-        <v>379</v>
-      </c>
       <c r="C212" t="s">
-        <v>107</v>
-      </c>
-      <c r="D212" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E212" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F212" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G212">
         <v>1</v>
@@ -7551,22 +6939,19 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
+        <v>379</v>
+      </c>
+      <c r="B213" t="s">
         <v>380</v>
       </c>
-      <c r="B213" t="s">
-        <v>381</v>
-      </c>
       <c r="C213" t="s">
-        <v>107</v>
-      </c>
-      <c r="D213" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E213" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F213" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G213">
         <v>1</v>
@@ -7577,23 +6962,20 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B214" t="s">
+        <v>381</v>
+      </c>
+      <c r="C214" t="s">
+        <v>106</v>
+      </c>
+      <c r="E214" t="s">
+        <v>133</v>
+      </c>
+      <c r="F214" t="s">
         <v>382</v>
       </c>
-      <c r="C214" t="s">
-        <v>107</v>
-      </c>
-      <c r="D214" t="s">
-        <v>5</v>
-      </c>
-      <c r="E214" t="s">
-        <v>134</v>
-      </c>
-      <c r="F214" t="s">
-        <v>383</v>
-      </c>
       <c r="G214">
         <v>1</v>
       </c>
@@ -7601,7 +6983,7 @@
         <v>1</v>
       </c>
       <c r="I214" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J214" t="s">
         <v>4</v>
@@ -7609,48 +6991,48 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B215" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C215" t="s">
-        <v>107</v>
-      </c>
-      <c r="D215" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E215" t="s">
+        <v>8</v>
+      </c>
+      <c r="F215" t="s">
         <v>9</v>
       </c>
-      <c r="F215" t="s">
-        <v>10</v>
-      </c>
       <c r="G215">
         <v>1</v>
       </c>
       <c r="H215">
         <v>1</v>
+      </c>
+      <c r="I215" t="s">
+        <v>122</v>
+      </c>
+      <c r="J215" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>90</v>
+        <v>383</v>
       </c>
       <c r="B216" t="s">
-        <v>91</v>
+        <v>384</v>
       </c>
       <c r="C216" t="s">
-        <v>107</v>
-      </c>
-      <c r="D216" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="E216" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="F216" t="s">
-        <v>10</v>
+        <v>139</v>
       </c>
       <c r="G216">
         <v>1</v>
@@ -7658,15 +7040,14 @@
       <c r="H216">
         <v>1</v>
       </c>
-      <c r="I216" t="s">
-        <v>123</v>
-      </c>
-      <c r="J216" t="s">
-        <v>26</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J216" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J216" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J216">
+      <sortCondition descending="1" ref="G2:G216"/>
+      <sortCondition ref="A2:A216"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
